--- a/S158_127/1.0.0/S-158_127_1_0_0_20260323.xlsx
+++ b/S158_127/1.0.0/S-158_127_1_0_0_20260323.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\work\git\S-127-Product-Specification-Development\S158_127\1.0.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F02B534A-49A5-4FC8-8FD8-77B0545678F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A30E0CA-5B83-4DD0-96F2-7A2571AABB92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="28110" windowHeight="18240" tabRatio="647" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">S127Checks!$K$1:$K$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">S127Checks!$K$1:$K$112</definedName>
     <definedName name="S101_Disposition">[1]Lists!$A$1:$A$3</definedName>
   </definedNames>
   <calcPr calcId="191029" iterate="1" iterateCount="1000" concurrentCalc="0"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="350">
   <si>
     <t>Document Number</t>
   </si>
@@ -709,9 +709,6 @@
     <t>Modified to reflect use of file-less cancellation</t>
   </si>
   <si>
-    <t>2.4.8.2</t>
-  </si>
-  <si>
     <t>2.5.5.6</t>
   </si>
   <si>
@@ -742,12 +739,6 @@
     <t>[7.4]; [2.6.10]</t>
   </si>
   <si>
-    <t>[12.16]; [5.2.1]</t>
-  </si>
-  <si>
-    <t>various</t>
-  </si>
-  <si>
     <t>Encoding instructions for features and information types using attribute information</t>
   </si>
   <si>
@@ -838,15 +829,6 @@
     <t>Amend fileLocator value</t>
   </si>
   <si>
-    <t>Complex attribute sourceIndication must have at least one sub-attribute populated</t>
-  </si>
-  <si>
-    <t>For each complex attribute sourceIndication with none of its sub-attributes populated</t>
-  </si>
-  <si>
-    <t>Delete or amend sourceIndication</t>
-  </si>
-  <si>
     <t>Repeated attribute value</t>
   </si>
   <si>
@@ -880,9 +862,6 @@
     <t>Correct values of maximum and minimum display scales.</t>
   </si>
   <si>
-    <t>4.4.1</t>
-  </si>
-  <si>
     <t>Dataset contains overlapping DataCoverage features.</t>
   </si>
   <si>
@@ -934,9 +913,6 @@
     <t>Remove prohibited association.</t>
   </si>
   <si>
-    <t>14.1</t>
-  </si>
-  <si>
     <t>Prohibited vertical uncertainty attribute of SpatialQuality for curve spatial object.</t>
   </si>
   <si>
@@ -980,9 +956,6 @@
   </si>
   <si>
     <t>Value required for mandatory attribute</t>
-  </si>
-  <si>
-    <t>For each attribute binding listed in in DCEG clause 2.4 as not nillableAND which is not populated</t>
   </si>
   <si>
     <t>Populate attribute</t>
@@ -1128,6 +1101,39 @@
   <si>
     <t>Producers may further restrict allowed values of nilReason.</t>
   </si>
+  <si>
+    <t>12.10</t>
+  </si>
+  <si>
+    <t>[12.13]; [5.2.1]</t>
+  </si>
+  <si>
+    <t>2.4.8.2, 22.19</t>
+  </si>
+  <si>
+    <t>5.2.1, 22.8, various</t>
+  </si>
+  <si>
+    <t>12.1.1, 14.4.2</t>
+  </si>
+  <si>
+    <t>4.3.2</t>
+  </si>
+  <si>
+    <t>4.3.1</t>
+  </si>
+  <si>
+    <t>17.1</t>
+  </si>
+  <si>
+    <t>12.1.2</t>
+  </si>
+  <si>
+    <t>For each attribute binding listed in in DCEG clause 2.4 as not nillable AND which is not populated</t>
+  </si>
+  <si>
+    <t>2.4.4</t>
+  </si>
 </sst>
 </file>
 
@@ -1149,7 +1155,7 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1157,7 +1163,7 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1165,7 +1171,7 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1173,21 +1179,21 @@
       <sz val="12"/>
       <color theme="9" tint="-0.249977111117893"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1476,7 +1482,7 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1553,9 +1559,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1572,9 +1575,6 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1618,12 +1618,24 @@
     <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1636,20 +1648,20 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1959,14 +1971,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="33.6" customHeight="1">
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="63" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="63"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="65"/>
       <c r="H2" s="25"/>
     </row>
     <row r="3" spans="2:8" s="1" customFormat="1" ht="20.45" customHeight="1">
@@ -1985,7 +1997,7 @@
       <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="37" t="s">
+      <c r="C4" s="36" t="s">
         <v>30</v>
       </c>
       <c r="D4" s="6"/>
@@ -2092,7 +2104,7 @@
       <c r="G12" s="26"/>
     </row>
     <row r="13" spans="2:8" s="1" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B13" s="64" t="s">
+      <c r="B13" s="66" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="5" t="s">
@@ -2106,7 +2118,7 @@
       <c r="G13" s="26"/>
     </row>
     <row r="14" spans="2:8" s="1" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B14" s="64"/>
+      <c r="B14" s="66"/>
       <c r="C14" s="15" t="s">
         <v>34</v>
       </c>
@@ -2118,7 +2130,7 @@
       <c r="G14" s="26"/>
     </row>
     <row r="15" spans="2:8" s="1" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B15" s="64"/>
+      <c r="B15" s="66"/>
       <c r="C15" s="16" t="s">
         <v>35</v>
       </c>
@@ -2130,11 +2142,11 @@
       <c r="G15" s="26"/>
     </row>
     <row r="16" spans="2:8" s="1" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B16" s="64"/>
-      <c r="C16" s="38" t="s">
+      <c r="B16" s="66"/>
+      <c r="C16" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="39" t="s">
+      <c r="D16" s="38" t="s">
         <v>28</v>
       </c>
       <c r="E16" s="18"/>
@@ -2142,7 +2154,7 @@
       <c r="G16" s="26"/>
     </row>
     <row r="17" spans="2:7" s="1" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B17" s="64"/>
+      <c r="B17" s="66"/>
       <c r="C17" s="17"/>
       <c r="D17" s="18"/>
       <c r="E17" s="18"/>
@@ -2150,7 +2162,7 @@
       <c r="G17" s="26"/>
     </row>
     <row r="18" spans="2:7" s="1" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B18" s="64"/>
+      <c r="B18" s="66"/>
       <c r="C18" s="19"/>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
@@ -2188,2571 +2200,2540 @@
   <dimension ref="A1:M138"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="13.5" thickBottom="1"/>
   <cols>
-    <col min="1" max="1" width="13" style="47" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" style="51" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" style="47" customWidth="1"/>
-    <col min="4" max="4" width="42.28515625" style="45" customWidth="1"/>
-    <col min="5" max="5" width="58.85546875" style="45" customWidth="1"/>
-    <col min="6" max="6" width="34.7109375" style="45" customWidth="1"/>
-    <col min="7" max="7" width="18.140625" style="54" customWidth="1"/>
-    <col min="8" max="8" width="16.28515625" style="47" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" style="49" customWidth="1"/>
-    <col min="10" max="10" width="8.28515625" style="49" customWidth="1"/>
-    <col min="11" max="11" width="8" style="49" customWidth="1"/>
-    <col min="12" max="12" width="9.42578125" style="45" customWidth="1"/>
-    <col min="13" max="13" width="25.85546875" style="45" customWidth="1"/>
+    <col min="1" max="1" width="13" style="45" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" style="49" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="45" customWidth="1"/>
+    <col min="4" max="4" width="42.28515625" style="43" customWidth="1"/>
+    <col min="5" max="5" width="58.85546875" style="43" customWidth="1"/>
+    <col min="6" max="6" width="34.7109375" style="43" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" style="52" customWidth="1"/>
+    <col min="8" max="8" width="16.28515625" style="69" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" style="47" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" style="47" customWidth="1"/>
+    <col min="11" max="11" width="8" style="47" customWidth="1"/>
+    <col min="12" max="12" width="9.42578125" style="43" customWidth="1"/>
+    <col min="13" max="13" width="25.85546875" style="43" customWidth="1"/>
     <col min="14" max="16384" width="8.7109375" style="35"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="26.25" thickBot="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="58" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="65" t="s">
+      <c r="C1" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="65" t="s">
+      <c r="D1" s="58" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="65" t="s">
+      <c r="E1" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="65" t="s">
+      <c r="F1" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="42" t="s">
+      <c r="G1" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="36" t="s">
+      <c r="H1" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="66" t="s">
+      <c r="I1" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="66" t="s">
+      <c r="J1" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="K1" s="66" t="s">
+      <c r="K1" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="L1" s="41" t="s">
+      <c r="L1" s="40" t="s">
         <v>149</v>
       </c>
-      <c r="M1" s="41" t="s">
+      <c r="M1" s="40" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="26.25" thickBot="1">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="42" t="s">
         <v>151</v>
       </c>
-      <c r="B2" s="44" t="str">
+      <c r="B2" s="42" t="str">
         <f>_xlfn.CONCAT("127_", TEXT(ROW()-1, "0000"))</f>
         <v>127_0001</v>
       </c>
-      <c r="C2" s="44" t="s">
+      <c r="C2" s="42" t="s">
         <v>200</v>
       </c>
-      <c r="D2" s="50" t="s">
+      <c r="D2" s="48" t="s">
         <v>71</v>
       </c>
-      <c r="E2" s="50" t="s">
+      <c r="E2" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="F2" s="50" t="s">
+      <c r="F2" s="48" t="s">
         <v>105</v>
       </c>
-      <c r="G2" s="50" t="s">
+      <c r="G2" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="H2" s="44">
+      <c r="H2" s="68">
         <v>7.3</v>
       </c>
-      <c r="I2" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L2" s="45" t="s">
+      <c r="I2" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L2" s="43" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="26.25" thickBot="1">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="B3" s="44" t="str">
+      <c r="B3" s="42" t="str">
         <f t="shared" ref="B3:B40" si="0">_xlfn.CONCAT("127_", TEXT(ROW()-1, "0000"))</f>
         <v>127_0002</v>
       </c>
-      <c r="C3" s="51" t="s">
+      <c r="C3" s="49" t="s">
         <v>200</v>
       </c>
-      <c r="D3" s="50" t="s">
-        <v>333</v>
-      </c>
-      <c r="E3" s="50" t="s">
-        <v>334</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>335</v>
-      </c>
-      <c r="G3" s="50" t="s">
+      <c r="D3" s="48" t="s">
+        <v>324</v>
+      </c>
+      <c r="E3" s="48" t="s">
+        <v>325</v>
+      </c>
+      <c r="F3" s="48" t="s">
+        <v>326</v>
+      </c>
+      <c r="G3" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="H3" s="44">
+      <c r="H3" s="68">
         <v>12.8</v>
       </c>
-      <c r="I3" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" s="45" t="s">
+      <c r="I3" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="43" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="39" thickBot="1">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="42" t="s">
         <v>153</v>
       </c>
-      <c r="B4" s="44" t="str">
+      <c r="B4" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0003</v>
       </c>
-      <c r="C4" s="51" t="s">
+      <c r="C4" s="49" t="s">
         <v>201</v>
       </c>
-      <c r="D4" s="50" t="s">
-        <v>336</v>
-      </c>
-      <c r="E4" s="50" t="s">
+      <c r="D4" s="48" t="s">
+        <v>327</v>
+      </c>
+      <c r="E4" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="50" t="s">
+      <c r="F4" s="48" t="s">
         <v>106</v>
       </c>
-      <c r="G4" s="50" t="s">
+      <c r="G4" s="48" t="s">
         <v>198</v>
       </c>
-      <c r="H4" s="44">
+      <c r="H4" s="68">
         <v>4.2</v>
       </c>
-      <c r="I4" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" s="45" t="s">
+      <c r="I4" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" s="43" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="39" thickBot="1">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="42" t="s">
         <v>154</v>
       </c>
-      <c r="B5" s="44" t="str">
+      <c r="B5" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0004</v>
       </c>
-      <c r="C5" s="51" t="s">
+      <c r="C5" s="49" t="s">
         <v>202</v>
       </c>
-      <c r="D5" s="52" t="s">
-        <v>228</v>
-      </c>
-      <c r="E5" s="52" t="s">
+      <c r="D5" s="50" t="s">
+        <v>227</v>
+      </c>
+      <c r="E5" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="52" t="s">
+      <c r="F5" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="G5" s="50" t="s">
+      <c r="G5" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="H5" s="44">
+      <c r="H5" s="68">
         <v>12.4</v>
       </c>
-      <c r="I5" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="J5" s="45"/>
-      <c r="K5" s="45"/>
-      <c r="L5" s="45" t="s">
+      <c r="I5" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
+      <c r="L5" s="43" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="26.25" thickBot="1">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="42" t="s">
         <v>155</v>
       </c>
-      <c r="B6" s="44" t="str">
+      <c r="B6" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0005</v>
       </c>
-      <c r="C6" s="51" t="s">
+      <c r="C6" s="49" t="s">
         <v>202</v>
       </c>
-      <c r="D6" s="52" t="s">
+      <c r="D6" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="52" t="s">
+      <c r="E6" s="50" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="52" t="s">
+      <c r="F6" s="50" t="s">
         <v>108</v>
       </c>
-      <c r="G6" s="50" t="s">
+      <c r="G6" s="48" t="s">
         <v>199</v>
       </c>
-      <c r="H6" s="44" t="s">
+      <c r="H6" s="68" t="s">
         <v>203</v>
       </c>
-      <c r="I6" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="J6" s="45"/>
-      <c r="K6" s="45"/>
-      <c r="L6" s="45" t="s">
+      <c r="I6" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="43"/>
+      <c r="K6" s="43"/>
+      <c r="L6" s="43" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="39" thickBot="1">
-      <c r="A7" s="44" t="s">
+      <c r="A7" s="42" t="s">
         <v>156</v>
       </c>
-      <c r="B7" s="44" t="str">
+      <c r="B7" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0006</v>
       </c>
-      <c r="C7" s="44" t="s">
+      <c r="C7" s="42" t="s">
         <v>200</v>
       </c>
-      <c r="D7" s="55" t="s">
+      <c r="D7" s="53" t="s">
         <v>204</v>
       </c>
-      <c r="E7" s="50" t="s">
-        <v>337</v>
-      </c>
-      <c r="F7" s="53" t="s">
+      <c r="E7" s="48" t="s">
+        <v>328</v>
+      </c>
+      <c r="F7" s="51" t="s">
         <v>109</v>
       </c>
-      <c r="G7" s="50" t="s">
+      <c r="G7" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="H7" s="44">
+      <c r="H7" s="68">
         <v>12.5</v>
       </c>
-      <c r="I7" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="J7" s="45" t="s">
+      <c r="I7" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" s="43" t="s">
         <v>195</v>
       </c>
-      <c r="K7" s="45"/>
-      <c r="L7" s="45" t="s">
+      <c r="K7" s="43"/>
+      <c r="L7" s="43" t="s">
         <v>147</v>
       </c>
-      <c r="M7" s="45" t="s">
+      <c r="M7" s="43" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="39" thickBot="1">
-      <c r="A8" s="44" t="s">
+      <c r="A8" s="42" t="s">
         <v>157</v>
       </c>
-      <c r="B8" s="44" t="str">
+      <c r="B8" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0007</v>
       </c>
-      <c r="C8" s="44" t="s">
+      <c r="C8" s="42" t="s">
         <v>200</v>
       </c>
-      <c r="D8" s="55" t="s">
+      <c r="D8" s="53" t="s">
         <v>206</v>
       </c>
-      <c r="E8" s="55" t="s">
-        <v>338</v>
-      </c>
-      <c r="F8" s="58" t="s">
+      <c r="E8" s="53" t="s">
+        <v>329</v>
+      </c>
+      <c r="F8" s="56" t="s">
         <v>110</v>
       </c>
-      <c r="G8" s="55" t="s">
+      <c r="G8" s="53" t="s">
         <v>198</v>
       </c>
-      <c r="H8" s="44" t="s">
+      <c r="H8" s="68" t="s">
         <v>208</v>
       </c>
-      <c r="I8" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="J8" s="45" t="s">
+      <c r="I8" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" s="43" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="45"/>
-      <c r="L8" s="45" t="s">
+      <c r="K8" s="43"/>
+      <c r="L8" s="43" t="s">
         <v>147</v>
       </c>
-      <c r="M8" s="45" t="s">
+      <c r="M8" s="43" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="39" thickBot="1">
-      <c r="A9" s="44" t="s">
+      <c r="A9" s="42" t="s">
         <v>158</v>
       </c>
-      <c r="B9" s="44" t="str">
+      <c r="B9" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0008</v>
       </c>
-      <c r="C9" s="44" t="s">
+      <c r="C9" s="42" t="s">
         <v>202</v>
       </c>
-      <c r="D9" s="55" t="s">
+      <c r="D9" s="53" t="s">
         <v>207</v>
       </c>
-      <c r="E9" s="50" t="s">
+      <c r="E9" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="50" t="s">
+      <c r="F9" s="48" t="s">
         <v>111</v>
       </c>
-      <c r="G9" s="55" t="s">
+      <c r="G9" s="53" t="s">
         <v>209</v>
       </c>
-      <c r="H9" s="44"/>
-      <c r="I9" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="J9" s="49" t="s">
+      <c r="H9" s="68"/>
+      <c r="I9" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" s="47" t="s">
         <v>195</v>
       </c>
-      <c r="L9" s="45" t="s">
+      <c r="L9" s="43" t="s">
         <v>147</v>
       </c>
-      <c r="M9" s="45" t="s">
+      <c r="M9" s="43" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="39" thickBot="1">
-      <c r="A10" s="44" t="s">
+      <c r="A10" s="42" t="s">
         <v>159</v>
       </c>
-      <c r="B10" s="44" t="str">
+      <c r="B10" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0009</v>
       </c>
-      <c r="C10" s="51" t="s">
+      <c r="C10" s="49" t="s">
         <v>202</v>
       </c>
-      <c r="D10" s="50" t="s">
+      <c r="D10" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="E10" s="50" t="s">
+      <c r="E10" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="50" t="s">
+      <c r="F10" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="G10" s="55" t="s">
+      <c r="G10" s="53" t="s">
         <v>209</v>
       </c>
-      <c r="H10" s="44"/>
-      <c r="I10" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L10" s="45" t="s">
+      <c r="H10" s="68"/>
+      <c r="I10" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L10" s="43" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="39" thickBot="1">
-      <c r="A11" s="44" t="s">
+      <c r="A11" s="42" t="s">
         <v>160</v>
       </c>
-      <c r="B11" s="44" t="str">
+      <c r="B11" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0010</v>
       </c>
-      <c r="C11" s="44" t="s">
+      <c r="C11" s="42" t="s">
         <v>202</v>
       </c>
-      <c r="D11" s="50" t="s">
+      <c r="D11" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="E11" s="50" t="s">
+      <c r="E11" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="50" t="s">
+      <c r="F11" s="48" t="s">
         <v>113</v>
       </c>
-      <c r="G11" s="55" t="s">
+      <c r="G11" s="53" t="s">
         <v>197</v>
       </c>
-      <c r="H11" s="44">
+      <c r="H11" s="68">
         <v>3</v>
       </c>
-      <c r="I11" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L11" s="45" t="s">
+      <c r="I11" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L11" s="43" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="39" thickBot="1">
-      <c r="A12" s="44" t="s">
+      <c r="A12" s="42" t="s">
         <v>161</v>
       </c>
-      <c r="B12" s="44" t="str">
+      <c r="B12" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0011</v>
       </c>
-      <c r="C12" s="44" t="s">
+      <c r="C12" s="42" t="s">
         <v>202</v>
       </c>
-      <c r="D12" s="50" t="s">
+      <c r="D12" s="48" t="s">
         <v>75</v>
       </c>
-      <c r="E12" s="50" t="s">
+      <c r="E12" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="F12" s="50" t="s">
+      <c r="F12" s="48" t="s">
         <v>114</v>
       </c>
-      <c r="G12" s="55" t="s">
+      <c r="G12" s="53" t="s">
         <v>197</v>
       </c>
-      <c r="H12" s="44">
+      <c r="H12" s="68">
         <v>3</v>
       </c>
-      <c r="I12" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L12" s="45" t="s">
+      <c r="I12" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L12" s="43" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="26.25" thickBot="1">
-      <c r="A13" s="44" t="s">
+      <c r="A13" s="42" t="s">
         <v>162</v>
       </c>
-      <c r="B13" s="44" t="str">
+      <c r="B13" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0012</v>
       </c>
-      <c r="C13" s="44" t="s">
+      <c r="C13" s="42" t="s">
         <v>201</v>
       </c>
-      <c r="D13" s="55" t="s">
+      <c r="D13" s="53" t="s">
         <v>214</v>
       </c>
-      <c r="E13" s="55" t="s">
+      <c r="E13" s="53" t="s">
         <v>213</v>
       </c>
-      <c r="F13" s="56" t="s">
-        <v>304</v>
-      </c>
-      <c r="G13" s="50" t="s">
+      <c r="F13" s="54" t="s">
+        <v>296</v>
+      </c>
+      <c r="G13" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="H13" s="44" t="s">
-        <v>271</v>
-      </c>
-      <c r="I13" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L13" s="45" t="s">
+      <c r="H13" s="68" t="s">
+        <v>265</v>
+      </c>
+      <c r="I13" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L13" s="43" t="s">
         <v>147</v>
       </c>
-      <c r="M13" s="45" t="s">
+      <c r="M13" s="43" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="26.25" thickBot="1">
-      <c r="A14" s="44" t="s">
+      <c r="A14" s="42" t="s">
         <v>163</v>
       </c>
-      <c r="B14" s="44" t="str">
+      <c r="B14" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0013</v>
       </c>
-      <c r="C14" s="51" t="s">
+      <c r="C14" s="49" t="s">
         <v>200</v>
       </c>
-      <c r="D14" s="50" t="s">
+      <c r="D14" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="E14" s="50" t="s">
-        <v>303</v>
-      </c>
-      <c r="F14" s="50" t="s">
+      <c r="E14" s="48" t="s">
+        <v>295</v>
+      </c>
+      <c r="F14" s="48" t="s">
         <v>115</v>
       </c>
-      <c r="G14" s="55" t="s">
+      <c r="G14" s="53" t="s">
         <v>199</v>
       </c>
-      <c r="H14" s="44" t="s">
-        <v>229</v>
-      </c>
-      <c r="I14" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L14" s="45" t="s">
+      <c r="H14" s="68" t="s">
+        <v>228</v>
+      </c>
+      <c r="I14" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L14" s="43" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="26.25" thickBot="1">
-      <c r="A15" s="44" t="s">
+      <c r="A15" s="42" t="s">
         <v>164</v>
       </c>
-      <c r="B15" s="44" t="str">
+      <c r="B15" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0014</v>
       </c>
-      <c r="C15" s="44" t="s">
+      <c r="C15" s="42" t="s">
         <v>202</v>
       </c>
-      <c r="D15" s="50" t="s">
+      <c r="D15" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="E15" s="50" t="s">
+      <c r="E15" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="50" t="s">
+      <c r="F15" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="G15" s="50" t="s">
+      <c r="G15" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="H15" s="44">
+      <c r="H15" s="68">
         <v>12.9</v>
       </c>
-      <c r="I15" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L15" s="45" t="s">
+      <c r="I15" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L15" s="43" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="16" spans="1:13" thickBot="1">
-      <c r="A16" s="44" t="s">
+      <c r="A16" s="42" t="s">
         <v>165</v>
       </c>
-      <c r="B16" s="44" t="str">
+      <c r="B16" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0015</v>
       </c>
-      <c r="C16" s="51" t="s">
+      <c r="C16" s="49" t="s">
         <v>202</v>
       </c>
-      <c r="D16" s="50" t="s">
+      <c r="D16" s="48" t="s">
         <v>78</v>
       </c>
-      <c r="E16" s="50" t="s">
+      <c r="E16" s="48" t="s">
         <v>46</v>
       </c>
-      <c r="F16" s="50" t="s">
+      <c r="F16" s="48" t="s">
         <v>117</v>
       </c>
-      <c r="G16" s="50" t="s">
+      <c r="G16" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="H16" s="44">
-        <v>12.1</v>
-      </c>
-      <c r="I16" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="J16" s="49" t="s">
+      <c r="H16" s="68" t="s">
+        <v>339</v>
+      </c>
+      <c r="I16" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="J16" s="47" t="s">
         <v>195</v>
       </c>
-      <c r="L16" s="45" t="s">
+      <c r="L16" s="43" t="s">
         <v>147</v>
       </c>
-      <c r="M16" s="45" t="s">
+      <c r="M16" s="43" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="39" thickBot="1">
-      <c r="A17" s="44" t="s">
+      <c r="A17" s="42" t="s">
         <v>166</v>
       </c>
-      <c r="B17" s="44" t="str">
+      <c r="B17" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0016</v>
       </c>
-      <c r="C17" s="51" t="s">
+      <c r="C17" s="49" t="s">
         <v>202</v>
       </c>
-      <c r="D17" s="50" t="s">
+      <c r="D17" s="48" t="s">
         <v>79</v>
       </c>
-      <c r="E17" s="50" t="s">
+      <c r="E17" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="50" t="s">
+      <c r="F17" s="48" t="s">
         <v>118</v>
       </c>
-      <c r="G17" s="50" t="s">
+      <c r="G17" s="48" t="s">
         <v>198</v>
       </c>
-      <c r="H17" s="44" t="s">
-        <v>230</v>
-      </c>
-      <c r="I17" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L17" s="45" t="s">
+      <c r="H17" s="68" t="s">
+        <v>229</v>
+      </c>
+      <c r="I17" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L17" s="43" t="s">
         <v>147</v>
       </c>
-      <c r="M17" s="45" t="s">
+      <c r="M17" s="43" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="26.25" thickBot="1">
-      <c r="A18" s="44" t="s">
+      <c r="A18" s="42" t="s">
         <v>167</v>
       </c>
-      <c r="B18" s="44" t="str">
+      <c r="B18" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0017</v>
       </c>
-      <c r="C18" s="51" t="s">
+      <c r="C18" s="49" t="s">
         <v>202</v>
       </c>
-      <c r="D18" s="48" t="s">
+      <c r="D18" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="E18" s="48" t="s">
-        <v>339</v>
-      </c>
-      <c r="F18" s="48" t="s">
+      <c r="E18" s="46" t="s">
+        <v>330</v>
+      </c>
+      <c r="F18" s="46" t="s">
         <v>119</v>
       </c>
-      <c r="G18" s="54" t="s">
+      <c r="G18" s="52" t="s">
         <v>197</v>
       </c>
-      <c r="H18" s="47" t="s">
-        <v>231</v>
-      </c>
-      <c r="I18" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L18" s="45" t="s">
+      <c r="H18" s="69" t="s">
+        <v>230</v>
+      </c>
+      <c r="I18" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L18" s="43" t="s">
         <v>147</v>
       </c>
-      <c r="M18" s="45" t="s">
+      <c r="M18" s="43" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="39" thickBot="1">
-      <c r="A19" s="44" t="s">
+      <c r="A19" s="42" t="s">
         <v>168</v>
       </c>
-      <c r="B19" s="44" t="str">
+      <c r="B19" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0018</v>
       </c>
-      <c r="C19" s="51" t="s">
+      <c r="C19" s="49" t="s">
         <v>202</v>
       </c>
-      <c r="D19" s="48" t="s">
+      <c r="D19" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="E19" s="48" t="s">
+      <c r="E19" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="F19" s="48" t="s">
+      <c r="F19" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="G19" s="55" t="s">
+      <c r="G19" s="53" t="s">
         <v>198</v>
       </c>
-      <c r="H19" s="47" t="s">
-        <v>272</v>
-      </c>
-      <c r="I19" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L19" s="45" t="s">
+      <c r="H19" s="69" t="s">
+        <v>266</v>
+      </c>
+      <c r="I19" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L19" s="43" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="51.75" thickBot="1">
-      <c r="A20" s="44" t="s">
+      <c r="A20" s="42" t="s">
         <v>169</v>
       </c>
-      <c r="B20" s="44" t="str">
+      <c r="B20" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0019</v>
       </c>
-      <c r="C20" s="51" t="s">
+      <c r="C20" s="49" t="s">
         <v>202</v>
       </c>
-      <c r="D20" s="48" t="s">
+      <c r="D20" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="E20" s="48" t="s">
+      <c r="E20" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="F20" s="48" t="s">
+      <c r="F20" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="G20" s="54" t="s">
+      <c r="G20" s="52" t="s">
         <v>198</v>
       </c>
-      <c r="H20" s="47" t="s">
-        <v>237</v>
-      </c>
-      <c r="I20" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L20" s="45" t="s">
+      <c r="H20" s="69" t="s">
+        <v>234</v>
+      </c>
+      <c r="I20" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L20" s="43" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="26.25" thickBot="1">
-      <c r="A21" s="44" t="s">
+      <c r="A21" s="42" t="s">
         <v>170</v>
       </c>
-      <c r="B21" s="44" t="str">
+      <c r="B21" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0020</v>
       </c>
-      <c r="C21" s="51" t="s">
+      <c r="C21" s="49" t="s">
         <v>201</v>
       </c>
-      <c r="D21" s="48" t="s">
+      <c r="D21" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="E21" s="48" t="s">
+      <c r="E21" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="F21" s="48" t="s">
+      <c r="F21" s="46" t="s">
         <v>123</v>
       </c>
-      <c r="G21" s="55" t="s">
+      <c r="G21" s="53" t="s">
         <v>197</v>
       </c>
-      <c r="H21" s="44">
+      <c r="H21" s="68">
         <v>13.1</v>
       </c>
-      <c r="I21" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L21" s="45" t="s">
+      <c r="I21" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L21" s="43" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="26.25" thickBot="1">
-      <c r="A22" s="44" t="s">
+      <c r="A22" s="42" t="s">
         <v>171</v>
       </c>
-      <c r="B22" s="44" t="str">
+      <c r="B22" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0021</v>
       </c>
-      <c r="C22" s="51" t="s">
+      <c r="C22" s="49" t="s">
         <v>201</v>
       </c>
-      <c r="D22" s="48" t="s">
+      <c r="D22" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="E22" s="48" t="s">
+      <c r="E22" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="F22" s="48" t="s">
+      <c r="F22" s="46" t="s">
         <v>124</v>
       </c>
-      <c r="G22" s="54" t="s">
+      <c r="G22" s="52" t="s">
         <v>197</v>
       </c>
-      <c r="H22" s="47">
+      <c r="H22" s="69">
         <v>13.1</v>
       </c>
-      <c r="I22" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L22" s="45" t="s">
+      <c r="I22" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L22" s="43" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="42" customHeight="1" thickBot="1">
-      <c r="A23" s="44" t="s">
+      <c r="A23" s="42" t="s">
         <v>172</v>
       </c>
-      <c r="B23" s="44" t="str">
+      <c r="B23" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0022</v>
       </c>
-      <c r="C23" s="51" t="s">
+      <c r="C23" s="49" t="s">
         <v>201</v>
       </c>
-      <c r="D23" s="48" t="s">
+      <c r="D23" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="E23" s="48" t="s">
-        <v>340</v>
-      </c>
-      <c r="F23" s="48" t="s">
+      <c r="E23" s="46" t="s">
+        <v>331</v>
+      </c>
+      <c r="F23" s="46" t="s">
         <v>122</v>
       </c>
-      <c r="G23" s="54" t="s">
+      <c r="G23" s="52" t="s">
         <v>197</v>
       </c>
-      <c r="H23" s="47">
+      <c r="H23" s="69">
         <v>14.1</v>
       </c>
-      <c r="I23" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="J23" s="49" t="s">
+      <c r="I23" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="J23" s="47" t="s">
         <v>195</v>
       </c>
-      <c r="L23" s="45" t="s">
+      <c r="L23" s="43" t="s">
         <v>147</v>
       </c>
-      <c r="M23" s="45" t="s">
+      <c r="M23" s="43" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="24" spans="1:13" thickBot="1">
-      <c r="A24" s="44" t="s">
+      <c r="A24" s="42" t="s">
         <v>173</v>
       </c>
-      <c r="B24" s="44" t="str">
+      <c r="B24" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0023</v>
       </c>
-      <c r="C24" s="51" t="s">
+      <c r="C24" s="49" t="s">
         <v>200</v>
       </c>
-      <c r="D24" s="48" t="s">
+      <c r="D24" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="E24" s="48" t="s">
+      <c r="E24" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="F24" s="48" t="s">
+      <c r="F24" s="46" t="s">
         <v>125</v>
       </c>
-      <c r="G24" s="55" t="s">
+      <c r="G24" s="53" t="s">
         <v>199</v>
       </c>
-      <c r="H24" s="44" t="s">
-        <v>232</v>
-      </c>
-      <c r="I24" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L24" s="45" t="s">
+      <c r="H24" s="68" t="s">
+        <v>231</v>
+      </c>
+      <c r="I24" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L24" s="43" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="26.25" thickBot="1">
-      <c r="A25" s="44" t="s">
+      <c r="A25" s="42" t="s">
         <v>174</v>
       </c>
-      <c r="B25" s="44" t="str">
+      <c r="B25" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0024</v>
       </c>
-      <c r="C25" s="51" t="s">
+      <c r="C25" s="49" t="s">
         <v>200</v>
       </c>
-      <c r="D25" s="48" t="s">
-        <v>341</v>
-      </c>
-      <c r="E25" s="48" t="s">
-        <v>342</v>
-      </c>
-      <c r="F25" s="48" t="s">
+      <c r="D25" s="46" t="s">
+        <v>332</v>
+      </c>
+      <c r="E25" s="46" t="s">
+        <v>333</v>
+      </c>
+      <c r="F25" s="46" t="s">
         <v>126</v>
       </c>
-      <c r="G25" s="54" t="s">
+      <c r="G25" s="52" t="s">
         <v>198</v>
       </c>
-      <c r="H25" s="47" t="s">
-        <v>230</v>
-      </c>
-      <c r="I25" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L25" s="45" t="s">
+      <c r="H25" s="69" t="s">
+        <v>229</v>
+      </c>
+      <c r="I25" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L25" s="43" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="26.25" thickBot="1">
-      <c r="A26" s="44" t="s">
+      <c r="A26" s="42" t="s">
         <v>175</v>
       </c>
-      <c r="B26" s="44" t="str">
+      <c r="B26" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0025</v>
       </c>
-      <c r="C26" s="51" t="s">
+      <c r="C26" s="49" t="s">
         <v>200</v>
       </c>
-      <c r="D26" s="48" t="s">
+      <c r="D26" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="E26" s="48" t="s">
+      <c r="E26" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="F26" s="48" t="s">
+      <c r="F26" s="46" t="s">
         <v>127</v>
       </c>
-      <c r="G26" s="55" t="s">
+      <c r="G26" s="53" t="s">
         <v>199</v>
       </c>
-      <c r="H26" s="44" t="s">
-        <v>233</v>
-      </c>
-      <c r="I26" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L26" s="45" t="s">
+      <c r="H26" s="68" t="s">
+        <v>340</v>
+      </c>
+      <c r="I26" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L26" s="43" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="26.25" thickBot="1">
-      <c r="A27" s="44" t="s">
+      <c r="A27" s="42" t="s">
         <v>176</v>
       </c>
-      <c r="B27" s="44" t="str">
+      <c r="B27" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0026</v>
       </c>
-      <c r="C27" s="51" t="s">
+      <c r="C27" s="49" t="s">
         <v>200</v>
       </c>
-      <c r="D27" s="48" t="s">
+      <c r="D27" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="E27" s="48" t="s">
+      <c r="E27" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="F27" s="48" t="s">
+      <c r="F27" s="46" t="s">
         <v>128</v>
       </c>
-      <c r="G27" s="54" t="s">
+      <c r="G27" s="52" t="s">
         <v>209</v>
       </c>
-      <c r="I27" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L27" s="45" t="s">
+      <c r="I27" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L27" s="43" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="26.25" thickBot="1">
-      <c r="A28" s="44" t="s">
+      <c r="A28" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="B28" s="44" t="str">
+      <c r="B28" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0027</v>
       </c>
-      <c r="C28" s="51" t="s">
+      <c r="C28" s="49" t="s">
         <v>200</v>
       </c>
-      <c r="D28" s="48" t="s">
+      <c r="D28" s="46" t="s">
         <v>89</v>
       </c>
-      <c r="E28" s="48" t="s">
+      <c r="E28" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="F28" s="48" t="s">
+      <c r="F28" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="G28" s="55" t="s">
+      <c r="G28" s="53" t="s">
         <v>198</v>
       </c>
-      <c r="H28" s="44" t="s">
-        <v>222</v>
-      </c>
-      <c r="I28" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L28" s="45" t="s">
+      <c r="H28" s="68" t="s">
+        <v>341</v>
+      </c>
+      <c r="I28" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L28" s="43" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="39" thickBot="1">
-      <c r="A29" s="44" t="s">
+      <c r="A29" s="42" t="s">
         <v>178</v>
       </c>
-      <c r="B29" s="44" t="str">
+      <c r="B29" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0028</v>
       </c>
-      <c r="C29" s="51" t="s">
+      <c r="C29" s="49" t="s">
         <v>200</v>
       </c>
-      <c r="D29" s="48" t="s">
+      <c r="D29" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="E29" s="48" t="s">
+      <c r="E29" s="46" t="s">
         <v>63</v>
       </c>
-      <c r="F29" s="48" t="s">
+      <c r="F29" s="46" t="s">
         <v>130</v>
       </c>
-      <c r="G29" s="55" t="s">
+      <c r="G29" s="53" t="s">
         <v>198</v>
       </c>
-      <c r="H29" s="47" t="s">
-        <v>236</v>
-      </c>
-      <c r="I29" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L29" s="45" t="s">
+      <c r="H29" s="69" t="s">
+        <v>342</v>
+      </c>
+      <c r="I29" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L29" s="43" t="s">
         <v>147</v>
       </c>
-      <c r="M29" s="45" t="s">
-        <v>235</v>
+      <c r="M29" s="43" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="39" thickBot="1">
-      <c r="A30" s="44" t="s">
+      <c r="A30" s="42" t="s">
         <v>179</v>
       </c>
-      <c r="B30" s="44" t="str">
+      <c r="B30" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0029</v>
       </c>
-      <c r="C30" s="51" t="s">
+      <c r="C30" s="49" t="s">
         <v>202</v>
       </c>
-      <c r="D30" s="48" t="s">
+      <c r="D30" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="E30" s="48" t="s">
+      <c r="E30" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="F30" s="48" t="s">
+      <c r="F30" s="46" t="s">
         <v>131</v>
       </c>
-      <c r="G30" s="55" t="s">
+      <c r="G30" s="53" t="s">
         <v>198</v>
       </c>
-      <c r="H30" s="47" t="s">
-        <v>236</v>
-      </c>
-      <c r="I30" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L30" s="45" t="s">
+      <c r="H30" s="69" t="s">
+        <v>233</v>
+      </c>
+      <c r="I30" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L30" s="43" t="s">
         <v>147</v>
       </c>
-      <c r="M30" s="45" t="s">
-        <v>235</v>
+      <c r="M30" s="43" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="26.25" thickBot="1">
-      <c r="A31" s="44" t="s">
+      <c r="A31" s="42" t="s">
         <v>180</v>
       </c>
-      <c r="B31" s="44" t="str">
+      <c r="B31" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0030</v>
       </c>
-      <c r="C31" s="51" t="s">
+      <c r="C31" s="49" t="s">
         <v>202</v>
       </c>
-      <c r="D31" s="48" t="s">
+      <c r="D31" s="46" t="s">
         <v>92</v>
       </c>
-      <c r="E31" s="48" t="s">
+      <c r="E31" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="F31" s="48" t="s">
+      <c r="F31" s="46" t="s">
         <v>132</v>
       </c>
-      <c r="G31" s="55" t="s">
+      <c r="G31" s="53" t="s">
         <v>198</v>
       </c>
-      <c r="H31" s="44" t="s">
-        <v>238</v>
-      </c>
-      <c r="I31" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L31" s="45" t="s">
+      <c r="H31" s="68" t="s">
+        <v>343</v>
+      </c>
+      <c r="I31" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L31" s="43" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="26.25" thickBot="1">
-      <c r="A32" s="44" t="s">
+      <c r="A32" s="42" t="s">
         <v>181</v>
       </c>
-      <c r="B32" s="44" t="str">
+      <c r="B32" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0031</v>
       </c>
-      <c r="C32" s="51" t="s">
+      <c r="C32" s="49" t="s">
         <v>200</v>
       </c>
-      <c r="D32" s="48" t="s">
+      <c r="D32" s="46" t="s">
         <v>93</v>
       </c>
-      <c r="E32" s="48" t="s">
+      <c r="E32" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="F32" s="48" t="s">
+      <c r="F32" s="46" t="s">
         <v>133</v>
       </c>
-      <c r="G32" s="55" t="s">
+      <c r="G32" s="53" t="s">
         <v>198</v>
       </c>
-      <c r="H32" s="47">
+      <c r="H32" s="69">
         <v>13.1</v>
       </c>
-      <c r="I32" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L32" s="45" t="s">
+      <c r="I32" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L32" s="43" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="26.25" thickBot="1">
-      <c r="A33" s="44" t="s">
+      <c r="A33" s="42" t="s">
         <v>182</v>
       </c>
-      <c r="B33" s="44" t="str">
+      <c r="B33" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0032</v>
       </c>
-      <c r="C33" s="51" t="s">
+      <c r="C33" s="49" t="s">
         <v>200</v>
       </c>
-      <c r="D33" s="48" t="s">
+      <c r="D33" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="E33" s="48" t="s">
+      <c r="E33" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="F33" s="48" t="s">
+      <c r="F33" s="46" t="s">
         <v>134</v>
       </c>
-      <c r="G33" s="55" t="s">
+      <c r="G33" s="53" t="s">
         <v>198</v>
       </c>
-      <c r="H33" s="44" t="s">
-        <v>305</v>
-      </c>
-      <c r="I33" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L33" s="45" t="s">
+      <c r="H33" s="68" t="s">
+        <v>297</v>
+      </c>
+      <c r="I33" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L33" s="43" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="26.25" thickBot="1">
-      <c r="A34" s="44" t="s">
+      <c r="A34" s="42" t="s">
         <v>183</v>
       </c>
-      <c r="B34" s="44" t="str">
+      <c r="B34" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0033</v>
       </c>
-      <c r="C34" s="51" t="s">
+      <c r="C34" s="49" t="s">
         <v>200</v>
       </c>
-      <c r="D34" s="48" t="s">
+      <c r="D34" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="E34" s="48" t="s">
+      <c r="E34" s="46" t="s">
         <v>68</v>
       </c>
-      <c r="F34" s="48" t="s">
+      <c r="F34" s="46" t="s">
         <v>135</v>
       </c>
-      <c r="G34" s="55" t="s">
+      <c r="G34" s="53" t="s">
         <v>198</v>
       </c>
-      <c r="H34" s="47">
+      <c r="H34" s="69">
         <v>14.6</v>
       </c>
-      <c r="I34" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L34" s="45" t="s">
+      <c r="I34" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L34" s="43" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="26.25" thickBot="1">
-      <c r="A35" s="44" t="s">
+      <c r="A35" s="42" t="s">
         <v>184</v>
       </c>
-      <c r="B35" s="44" t="str">
+      <c r="B35" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0034</v>
       </c>
-      <c r="C35" s="51" t="s">
+      <c r="C35" s="49" t="s">
         <v>200</v>
       </c>
-      <c r="D35" s="48" t="s">
+      <c r="D35" s="46" t="s">
         <v>96</v>
       </c>
-      <c r="E35" s="48" t="s">
+      <c r="E35" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="F35" s="48" t="s">
+      <c r="F35" s="46" t="s">
         <v>136</v>
       </c>
-      <c r="G35" s="55" t="s">
+      <c r="G35" s="53" t="s">
         <v>199</v>
       </c>
-      <c r="H35" s="47" t="s">
-        <v>239</v>
-      </c>
-      <c r="I35" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L35" s="45" t="s">
+      <c r="H35" s="69" t="s">
+        <v>236</v>
+      </c>
+      <c r="I35" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L35" s="43" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="39" thickBot="1">
-      <c r="A36" s="44" t="s">
+      <c r="A36" s="42" t="s">
         <v>185</v>
       </c>
-      <c r="B36" s="44" t="str">
+      <c r="B36" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0035</v>
       </c>
-      <c r="C36" s="51" t="s">
+      <c r="C36" s="49" t="s">
         <v>200</v>
       </c>
-      <c r="D36" s="48" t="s">
+      <c r="D36" s="46" t="s">
         <v>97</v>
       </c>
-      <c r="E36" s="48" t="s">
+      <c r="E36" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="F36" s="48" t="s">
+      <c r="F36" s="46" t="s">
         <v>137</v>
       </c>
-      <c r="G36" s="54" t="s">
+      <c r="G36" s="52" t="s">
         <v>198</v>
       </c>
-      <c r="H36" s="47" t="s">
-        <v>223</v>
-      </c>
-      <c r="I36" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L36" s="45" t="s">
+      <c r="H36" s="69" t="s">
+        <v>222</v>
+      </c>
+      <c r="I36" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L36" s="43" t="s">
         <v>145</v>
       </c>
-      <c r="M36" s="45" t="s">
-        <v>306</v>
+      <c r="M36" s="43" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="26.25" thickBot="1">
-      <c r="A37" s="44" t="s">
+      <c r="A37" s="42" t="s">
         <v>186</v>
       </c>
-      <c r="B37" s="44" t="str">
+      <c r="B37" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0036</v>
       </c>
-      <c r="C37" s="51" t="s">
+      <c r="C37" s="49" t="s">
         <v>202</v>
       </c>
-      <c r="D37" s="48" t="s">
+      <c r="D37" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="E37" s="55" t="s">
+      <c r="E37" s="53" t="s">
+        <v>223</v>
+      </c>
+      <c r="F37" s="46" t="s">
         <v>224</v>
       </c>
-      <c r="F37" s="48" t="s">
-        <v>225</v>
-      </c>
-      <c r="G37" s="55" t="s">
+      <c r="G37" s="53" t="s">
         <v>197</v>
       </c>
-      <c r="H37" s="47">
+      <c r="H37" s="69">
         <v>12.11</v>
       </c>
-      <c r="I37" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L37" s="45" t="s">
+      <c r="I37" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L37" s="43" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="39" thickBot="1">
-      <c r="A38" s="44" t="s">
+      <c r="A38" s="42" t="s">
         <v>187</v>
       </c>
-      <c r="B38" s="44" t="str">
+      <c r="B38" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0037</v>
       </c>
-      <c r="C38" s="51" t="s">
+      <c r="C38" s="49" t="s">
         <v>201</v>
       </c>
-      <c r="D38" s="55" t="s">
-        <v>226</v>
-      </c>
-      <c r="E38" s="48" t="s">
-        <v>343</v>
-      </c>
-      <c r="F38" s="48" t="s">
-        <v>344</v>
-      </c>
-      <c r="G38" s="55" t="s">
+      <c r="D38" s="53" t="s">
+        <v>225</v>
+      </c>
+      <c r="E38" s="46" t="s">
+        <v>334</v>
+      </c>
+      <c r="F38" s="46" t="s">
+        <v>335</v>
+      </c>
+      <c r="G38" s="53" t="s">
         <v>197</v>
       </c>
-      <c r="H38" s="44">
+      <c r="H38" s="68">
         <v>7.5</v>
       </c>
-      <c r="I38" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="J38" s="49" t="s">
+      <c r="I38" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="J38" s="47" t="s">
         <v>195</v>
       </c>
-      <c r="L38" s="45" t="s">
+      <c r="L38" s="43" t="s">
         <v>148</v>
       </c>
-      <c r="M38" s="45" t="s">
+      <c r="M38" s="43" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="39" thickBot="1">
-      <c r="A39" s="44" t="s">
+      <c r="A39" s="42" t="s">
         <v>188</v>
       </c>
-      <c r="B39" s="44" t="str">
+      <c r="B39" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0038</v>
       </c>
-      <c r="C39" s="51" t="s">
+      <c r="C39" s="49" t="s">
         <v>200</v>
       </c>
-      <c r="D39" s="48" t="s">
+      <c r="D39" s="46" t="s">
         <v>99</v>
       </c>
-      <c r="E39" s="48" t="s">
+      <c r="E39" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="F39" s="48" t="s">
+      <c r="F39" s="46" t="s">
         <v>138</v>
       </c>
-      <c r="G39" s="54" t="s">
+      <c r="G39" s="52" t="s">
         <v>198</v>
       </c>
-      <c r="H39" s="47" t="s">
-        <v>240</v>
-      </c>
-      <c r="I39" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L39" s="45" t="s">
+      <c r="H39" s="69" t="s">
+        <v>237</v>
+      </c>
+      <c r="I39" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L39" s="43" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="26.25" thickBot="1">
-      <c r="A40" s="44" t="s">
+      <c r="A40" s="42" t="s">
         <v>189</v>
       </c>
-      <c r="B40" s="44" t="str">
+      <c r="B40" s="42" t="str">
         <f t="shared" si="0"/>
         <v>127_0039</v>
       </c>
-      <c r="C40" s="51" t="s">
+      <c r="C40" s="49" t="s">
         <v>200</v>
       </c>
-      <c r="D40" s="48" t="s">
+      <c r="D40" s="46" t="s">
         <v>100</v>
       </c>
-      <c r="E40" s="48" t="s">
+      <c r="E40" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="F40" s="48" t="s">
+      <c r="F40" s="46" t="s">
         <v>139</v>
       </c>
-      <c r="G40" s="54" t="s">
+      <c r="G40" s="52" t="s">
         <v>198</v>
       </c>
-      <c r="H40" s="47" t="s">
-        <v>241</v>
-      </c>
-      <c r="I40" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L40" s="45" t="s">
+      <c r="H40" s="69" t="s">
+        <v>238</v>
+      </c>
+      <c r="I40" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L40" s="43" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="26.25" thickBot="1">
-      <c r="A41" s="44" t="s">
+      <c r="A41" s="42" t="s">
         <v>190</v>
       </c>
-      <c r="B41" s="44" t="str">
-        <f t="shared" ref="B41:B70" si="1">_xlfn.CONCAT("127_", TEXT(ROW()-1, "0000"))</f>
+      <c r="B41" s="42" t="str">
+        <f t="shared" ref="B41:B69" si="1">_xlfn.CONCAT("127_", TEXT(ROW()-1, "0000"))</f>
         <v>127_0040</v>
       </c>
-      <c r="C41" s="51" t="s">
+      <c r="C41" s="49" t="s">
         <v>200</v>
       </c>
-      <c r="D41" s="48" t="s">
+      <c r="D41" s="46" t="s">
         <v>100</v>
       </c>
-      <c r="E41" s="48" t="s">
+      <c r="E41" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="F41" s="48" t="s">
+      <c r="F41" s="46" t="s">
         <v>140</v>
       </c>
-      <c r="G41" s="54" t="s">
+      <c r="G41" s="52" t="s">
         <v>198</v>
       </c>
-      <c r="H41" s="47" t="s">
-        <v>242</v>
-      </c>
-      <c r="I41" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L41" s="45" t="s">
+      <c r="H41" s="69" t="s">
+        <v>239</v>
+      </c>
+      <c r="I41" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L41" s="43" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="51.75" thickBot="1">
-      <c r="A42" s="44" t="s">
+      <c r="A42" s="42" t="s">
         <v>191</v>
       </c>
-      <c r="B42" s="44" t="str">
+      <c r="B42" s="42" t="str">
         <f t="shared" si="1"/>
         <v>127_0041</v>
       </c>
-      <c r="C42" s="51" t="s">
+      <c r="C42" s="49" t="s">
         <v>200</v>
       </c>
-      <c r="D42" s="48" t="s">
+      <c r="D42" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="E42" s="48" t="s">
+      <c r="E42" s="46" t="s">
         <v>56</v>
       </c>
-      <c r="F42" s="48" t="s">
+      <c r="F42" s="46" t="s">
         <v>141</v>
       </c>
-      <c r="G42" s="54" t="s">
+      <c r="G42" s="52" t="s">
         <v>198</v>
       </c>
-      <c r="H42" s="47" t="s">
-        <v>243</v>
-      </c>
-      <c r="I42" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L42" s="45" t="s">
+      <c r="H42" s="69" t="s">
+        <v>240</v>
+      </c>
+      <c r="I42" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L42" s="43" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="39" thickBot="1">
-      <c r="A43" s="44" t="s">
+      <c r="A43" s="42" t="s">
         <v>192</v>
       </c>
-      <c r="B43" s="44" t="str">
+      <c r="B43" s="42" t="str">
         <f t="shared" si="1"/>
         <v>127_0042</v>
       </c>
-      <c r="C43" s="51" t="s">
+      <c r="C43" s="49" t="s">
         <v>200</v>
       </c>
-      <c r="D43" s="48" t="s">
+      <c r="D43" s="46" t="s">
         <v>102</v>
       </c>
-      <c r="E43" s="48" t="s">
+      <c r="E43" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="F43" s="48" t="s">
+      <c r="F43" s="46" t="s">
         <v>142</v>
       </c>
-      <c r="G43" s="54" t="s">
+      <c r="G43" s="52" t="s">
         <v>197</v>
       </c>
-      <c r="H43" s="47" t="s">
-        <v>243</v>
-      </c>
-      <c r="I43" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L43" s="45" t="s">
+      <c r="H43" s="69" t="s">
+        <v>240</v>
+      </c>
+      <c r="I43" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L43" s="43" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="26.25" thickBot="1">
-      <c r="A44" s="44" t="s">
+      <c r="A44" s="42" t="s">
         <v>193</v>
       </c>
-      <c r="B44" s="44" t="str">
+      <c r="B44" s="42" t="str">
         <f t="shared" si="1"/>
         <v>127_0043</v>
       </c>
-      <c r="C44" s="51" t="s">
+      <c r="C44" s="49" t="s">
         <v>200</v>
       </c>
-      <c r="D44" s="48" t="s">
+      <c r="D44" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="E44" s="48" t="s">
+      <c r="E44" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="F44" s="48" t="s">
+      <c r="F44" s="46" t="s">
         <v>143</v>
       </c>
-      <c r="G44" s="54" t="s">
+      <c r="G44" s="52" t="s">
         <v>198</v>
       </c>
-      <c r="H44" s="47" t="s">
-        <v>227</v>
-      </c>
-      <c r="I44" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L44" s="45" t="s">
+      <c r="H44" s="69" t="s">
+        <v>226</v>
+      </c>
+      <c r="I44" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L44" s="43" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="39" thickBot="1">
-      <c r="A45" s="44" t="s">
+      <c r="A45" s="42" t="s">
         <v>194</v>
       </c>
-      <c r="B45" s="44" t="str">
+      <c r="B45" s="42" t="str">
         <f t="shared" si="1"/>
         <v>127_0044</v>
       </c>
-      <c r="C45" s="51" t="s">
+      <c r="C45" s="49" t="s">
         <v>202</v>
       </c>
-      <c r="D45" s="48" t="s">
+      <c r="D45" s="46" t="s">
         <v>104</v>
       </c>
-      <c r="E45" s="48" t="s">
+      <c r="E45" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F45" s="48" t="s">
+      <c r="F45" s="46" t="s">
         <v>144</v>
       </c>
-      <c r="G45" s="54" t="s">
+      <c r="G45" s="52" t="s">
         <v>198</v>
       </c>
-      <c r="H45" s="47" t="s">
-        <v>238</v>
-      </c>
-      <c r="I45" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L45" s="45" t="s">
+      <c r="H45" s="69" t="s">
+        <v>235</v>
+      </c>
+      <c r="I45" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L45" s="43" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="39" thickBot="1">
-      <c r="A46" s="44" t="str">
+      <c r="A46" s="42" t="str">
         <f>_xlfn.CONCAT("127_Ed2_", TEXT(ROW()-45, "000"))</f>
         <v>127_Ed2_001</v>
       </c>
-      <c r="B46" s="44" t="str">
+      <c r="B46" s="42" t="str">
         <f t="shared" si="1"/>
         <v>127_0045</v>
       </c>
-      <c r="C46" s="44" t="s">
+      <c r="C46" s="42" t="s">
         <v>201</v>
       </c>
-      <c r="D46" s="55" t="s">
+      <c r="D46" s="53" t="s">
         <v>218</v>
       </c>
-      <c r="E46" s="55" t="s">
+      <c r="E46" s="53" t="s">
         <v>219</v>
       </c>
-      <c r="F46" s="48" t="s">
+      <c r="F46" s="46" t="s">
         <v>220</v>
       </c>
-      <c r="G46" s="55" t="s">
+      <c r="G46" s="53" t="s">
         <v>197</v>
       </c>
-      <c r="H46" s="44">
+      <c r="H46" s="68">
         <v>13.1</v>
       </c>
-      <c r="I46" s="49" t="s">
+      <c r="I46" s="47" t="s">
         <v>195</v>
       </c>
-      <c r="L46" s="45" t="s">
+      <c r="L46" s="43" t="s">
         <v>209</v>
       </c>
-      <c r="M46" s="45" t="s">
-        <v>275</v>
+      <c r="M46" s="43" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="26.25" thickBot="1">
-      <c r="A47" s="44" t="str">
-        <f t="shared" ref="A47:A70" si="2">_xlfn.CONCAT("127_Ed2_", TEXT(ROW()-45, "000"))</f>
+      <c r="A47" s="42" t="str">
+        <f t="shared" ref="A47:A69" si="2">_xlfn.CONCAT("127_Ed2_", TEXT(ROW()-45, "000"))</f>
         <v>127_Ed2_002</v>
       </c>
-      <c r="B47" s="44" t="str">
+      <c r="B47" s="42" t="str">
         <f t="shared" si="1"/>
         <v>127_0046</v>
       </c>
-      <c r="C47" s="51" t="s">
+      <c r="C47" s="49" t="s">
         <v>200</v>
       </c>
-      <c r="D47" s="45" t="s">
+      <c r="D47" s="43" t="s">
+        <v>241</v>
+      </c>
+      <c r="E47" s="43" t="s">
+        <v>242</v>
+      </c>
+      <c r="F47" s="43" t="s">
+        <v>243</v>
+      </c>
+      <c r="G47" s="44" t="s">
+        <v>198</v>
+      </c>
+      <c r="H47" s="69" t="s">
         <v>244</v>
       </c>
-      <c r="E47" s="45" t="s">
+      <c r="I47" s="47" t="s">
+        <v>195</v>
+      </c>
+      <c r="L47" s="43" t="s">
         <v>245</v>
       </c>
-      <c r="F47" s="45" t="s">
-        <v>246</v>
-      </c>
-      <c r="G47" s="46" t="s">
-        <v>198</v>
-      </c>
-      <c r="H47" s="47" t="s">
-        <v>247</v>
-      </c>
-      <c r="I47" s="49" t="s">
-        <v>195</v>
-      </c>
-      <c r="L47" s="45" t="s">
-        <v>248</v>
-      </c>
     </row>
     <row r="48" spans="1:13" ht="26.25" thickBot="1">
-      <c r="A48" s="44" t="str">
+      <c r="A48" s="42" t="str">
         <f t="shared" si="2"/>
         <v>127_Ed2_003</v>
       </c>
-      <c r="B48" s="44" t="str">
+      <c r="B48" s="42" t="str">
         <f t="shared" si="1"/>
         <v>127_0047</v>
       </c>
-      <c r="C48" s="47" t="s">
+      <c r="C48" s="45" t="s">
         <v>202</v>
       </c>
-      <c r="D48" s="55" t="s">
-        <v>249</v>
-      </c>
-      <c r="E48" s="55" t="s">
-        <v>250</v>
-      </c>
-      <c r="F48" s="48" t="s">
-        <v>251</v>
-      </c>
-      <c r="G48" s="55" t="s">
+      <c r="D48" s="53" t="s">
+        <v>246</v>
+      </c>
+      <c r="E48" s="53" t="s">
+        <v>247</v>
+      </c>
+      <c r="F48" s="46" t="s">
+        <v>248</v>
+      </c>
+      <c r="G48" s="53" t="s">
         <v>197</v>
       </c>
-      <c r="H48" s="44">
+      <c r="H48" s="68">
         <v>7.3</v>
       </c>
-      <c r="I48" s="49" t="s">
+      <c r="I48" s="47" t="s">
         <v>195</v>
       </c>
-      <c r="L48" s="45" t="s">
-        <v>273</v>
+      <c r="L48" s="43" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="51.75" thickBot="1">
-      <c r="A49" s="44" t="str">
+      <c r="A49" s="42" t="str">
         <f t="shared" si="2"/>
         <v>127_Ed2_004</v>
       </c>
-      <c r="B49" s="44" t="str">
+      <c r="B49" s="42" t="str">
         <f t="shared" si="1"/>
         <v>127_0048</v>
       </c>
       <c r="C49" s="34" t="s">
         <v>200</v>
       </c>
-      <c r="D49" s="60" t="s">
-        <v>276</v>
-      </c>
-      <c r="E49" s="60" t="s">
-        <v>277</v>
-      </c>
-      <c r="F49" s="56" t="s">
-        <v>278</v>
-      </c>
-      <c r="G49" s="60" t="s">
+      <c r="D49" s="57" t="s">
+        <v>270</v>
+      </c>
+      <c r="E49" s="57" t="s">
+        <v>271</v>
+      </c>
+      <c r="F49" s="54" t="s">
+        <v>272</v>
+      </c>
+      <c r="G49" s="57" t="s">
         <v>198</v>
       </c>
-      <c r="H49" s="43" t="s">
-        <v>279</v>
-      </c>
-      <c r="I49" s="45" t="s">
+      <c r="H49" s="70" t="s">
+        <v>344</v>
+      </c>
+      <c r="I49" s="43" t="s">
         <v>195</v>
       </c>
-      <c r="L49" s="55" t="s">
-        <v>273</v>
+      <c r="L49" s="53" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="26.25" thickBot="1">
-      <c r="A50" s="44" t="str">
+      <c r="A50" s="42" t="str">
         <f t="shared" si="2"/>
         <v>127_Ed2_005</v>
       </c>
-      <c r="B50" s="44" t="str">
+      <c r="B50" s="42" t="str">
         <f t="shared" si="1"/>
         <v>127_0049</v>
       </c>
       <c r="C50" s="34" t="s">
         <v>200</v>
       </c>
-      <c r="D50" s="60" t="s">
-        <v>280</v>
-      </c>
-      <c r="E50" s="60" t="s">
-        <v>281</v>
-      </c>
-      <c r="F50" s="56" t="s">
-        <v>282</v>
-      </c>
-      <c r="G50" s="60" t="s">
+      <c r="D50" s="57" t="s">
+        <v>273</v>
+      </c>
+      <c r="E50" s="57" t="s">
+        <v>274</v>
+      </c>
+      <c r="F50" s="54" t="s">
+        <v>275</v>
+      </c>
+      <c r="G50" s="57" t="s">
         <v>198</v>
       </c>
-      <c r="H50" s="43" t="s">
-        <v>279</v>
-      </c>
-      <c r="I50" s="45" t="s">
+      <c r="H50" s="70" t="s">
+        <v>345</v>
+      </c>
+      <c r="I50" s="43" t="s">
         <v>195</v>
       </c>
-      <c r="L50" s="55" t="s">
-        <v>273</v>
+      <c r="L50" s="53" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="39" thickBot="1">
-      <c r="A51" s="44" t="str">
+      <c r="A51" s="42" t="str">
         <f t="shared" si="2"/>
         <v>127_Ed2_006</v>
       </c>
-      <c r="B51" s="44" t="str">
+      <c r="B51" s="42" t="str">
         <f t="shared" si="1"/>
         <v>127_0050</v>
       </c>
       <c r="C51" s="34" t="s">
         <v>200</v>
       </c>
-      <c r="D51" s="60" t="s">
-        <v>283</v>
-      </c>
-      <c r="E51" s="60" t="s">
-        <v>284</v>
-      </c>
-      <c r="F51" s="56" t="s">
-        <v>285</v>
-      </c>
-      <c r="G51" s="60" t="s">
+      <c r="D51" s="57" t="s">
+        <v>276</v>
+      </c>
+      <c r="E51" s="57" t="s">
+        <v>277</v>
+      </c>
+      <c r="F51" s="54" t="s">
+        <v>278</v>
+      </c>
+      <c r="G51" s="57" t="s">
         <v>198</v>
       </c>
-      <c r="H51" s="43" t="s">
-        <v>279</v>
-      </c>
-      <c r="I51" s="45" t="s">
+      <c r="H51" s="70" t="s">
+        <v>345</v>
+      </c>
+      <c r="I51" s="43" t="s">
         <v>195</v>
       </c>
-      <c r="L51" s="55" t="s">
-        <v>273</v>
+      <c r="L51" s="53" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="51.75" thickBot="1">
-      <c r="A52" s="44" t="str">
+      <c r="A52" s="42" t="str">
         <f t="shared" si="2"/>
         <v>127_Ed2_007</v>
       </c>
-      <c r="B52" s="44" t="str">
+      <c r="B52" s="42" t="str">
         <f t="shared" si="1"/>
         <v>127_0051</v>
       </c>
       <c r="C52" s="34" t="s">
         <v>202</v>
       </c>
-      <c r="D52" s="60" t="s">
-        <v>286</v>
-      </c>
-      <c r="E52" s="60" t="s">
-        <v>345</v>
-      </c>
-      <c r="F52" s="56" t="s">
-        <v>287</v>
-      </c>
-      <c r="G52" s="60"/>
-      <c r="H52" s="43"/>
-      <c r="I52" s="45" t="s">
+      <c r="D52" s="57" t="s">
+        <v>279</v>
+      </c>
+      <c r="E52" s="57" t="s">
+        <v>336</v>
+      </c>
+      <c r="F52" s="54" t="s">
+        <v>280</v>
+      </c>
+      <c r="G52" s="57" t="s">
+        <v>209</v>
+      </c>
+      <c r="H52" s="70"/>
+      <c r="I52" s="43" t="s">
         <v>195</v>
       </c>
-      <c r="L52" s="55" t="s">
+      <c r="L52" s="53" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="39" thickBot="1">
-      <c r="A53" s="44" t="str">
+      <c r="A53" s="42" t="str">
         <f t="shared" si="2"/>
         <v>127_Ed2_008</v>
       </c>
-      <c r="B53" s="44" t="str">
+      <c r="B53" s="42" t="str">
         <f t="shared" si="1"/>
         <v>127_0052</v>
       </c>
       <c r="C53" s="34" t="s">
         <v>202</v>
       </c>
-      <c r="D53" s="60" t="s">
-        <v>288</v>
-      </c>
-      <c r="E53" s="60" t="s">
-        <v>289</v>
-      </c>
-      <c r="F53" s="56" t="s">
-        <v>290</v>
-      </c>
-      <c r="G53" s="60" t="s">
+      <c r="D53" s="57" t="s">
+        <v>281</v>
+      </c>
+      <c r="E53" s="57" t="s">
+        <v>282</v>
+      </c>
+      <c r="F53" s="54" t="s">
+        <v>283</v>
+      </c>
+      <c r="G53" s="57" t="s">
         <v>198</v>
       </c>
-      <c r="H53" s="43" t="s">
-        <v>261</v>
-      </c>
-      <c r="I53" s="45" t="s">
+      <c r="H53" s="70" t="s">
+        <v>258</v>
+      </c>
+      <c r="I53" s="43" t="s">
         <v>195</v>
       </c>
-      <c r="L53" s="55" t="s">
+      <c r="L53" s="53" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="26.25" thickBot="1">
-      <c r="A54" s="44" t="str">
+      <c r="A54" s="42" t="str">
         <f t="shared" si="2"/>
         <v>127_Ed2_009</v>
       </c>
-      <c r="B54" s="44" t="str">
+      <c r="B54" s="42" t="str">
         <f t="shared" si="1"/>
         <v>127_0053</v>
       </c>
       <c r="C54" s="34" t="s">
         <v>202</v>
       </c>
-      <c r="D54" s="40" t="s">
-        <v>291</v>
-      </c>
-      <c r="E54" s="60" t="s">
-        <v>292</v>
-      </c>
-      <c r="F54" s="56" t="s">
-        <v>293</v>
-      </c>
-      <c r="G54" s="60" t="s">
+      <c r="D54" s="39" t="s">
+        <v>284</v>
+      </c>
+      <c r="E54" s="57" t="s">
+        <v>285</v>
+      </c>
+      <c r="F54" s="54" t="s">
+        <v>286</v>
+      </c>
+      <c r="G54" s="57" t="s">
         <v>198</v>
       </c>
-      <c r="H54" s="43" t="s">
-        <v>307</v>
-      </c>
-      <c r="I54" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L54" s="55" t="s">
+      <c r="H54" s="70" t="s">
+        <v>299</v>
+      </c>
+      <c r="I54" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L54" s="53" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="26.25" thickBot="1">
-      <c r="A55" s="44" t="str">
+      <c r="A55" s="42" t="str">
         <f t="shared" si="2"/>
         <v>127_Ed2_010</v>
       </c>
-      <c r="B55" s="44" t="str">
+      <c r="B55" s="42" t="str">
         <f t="shared" si="1"/>
         <v>127_0054</v>
       </c>
       <c r="C55" s="34" t="s">
         <v>202</v>
       </c>
-      <c r="D55" s="60" t="s">
-        <v>294</v>
-      </c>
-      <c r="E55" s="60" t="s">
-        <v>295</v>
-      </c>
-      <c r="F55" s="57" t="s">
-        <v>296</v>
-      </c>
-      <c r="G55" s="60" t="s">
+      <c r="D55" s="57" t="s">
+        <v>287</v>
+      </c>
+      <c r="E55" s="57" t="s">
+        <v>288</v>
+      </c>
+      <c r="F55" s="55" t="s">
+        <v>289</v>
+      </c>
+      <c r="G55" s="57" t="s">
         <v>198</v>
       </c>
-      <c r="H55" s="43" t="s">
-        <v>297</v>
-      </c>
-      <c r="I55" s="49" t="s">
-        <v>31</v>
-      </c>
-      <c r="L55" s="67" t="s">
+      <c r="H55" s="70" t="s">
+        <v>346</v>
+      </c>
+      <c r="I55" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="L55" s="60" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="39" thickBot="1">
-      <c r="A56" s="44" t="str">
+      <c r="A56" s="42" t="str">
         <f t="shared" si="2"/>
         <v>127_Ed2_011</v>
       </c>
-      <c r="B56" s="44" t="str">
+      <c r="B56" s="42" t="str">
         <f t="shared" si="1"/>
         <v>127_0055</v>
       </c>
       <c r="C56" s="34" t="s">
         <v>202</v>
       </c>
-      <c r="D56" s="60" t="s">
-        <v>298</v>
-      </c>
-      <c r="E56" s="60" t="s">
-        <v>299</v>
-      </c>
-      <c r="F56" s="57" t="s">
-        <v>296</v>
-      </c>
-      <c r="G56" s="60" t="s">
+      <c r="D56" s="57" t="s">
+        <v>290</v>
+      </c>
+      <c r="E56" s="57" t="s">
+        <v>291</v>
+      </c>
+      <c r="F56" s="55" t="s">
+        <v>289</v>
+      </c>
+      <c r="G56" s="57" t="s">
         <v>198</v>
       </c>
-      <c r="H56" s="43" t="s">
-        <v>297</v>
-      </c>
-      <c r="I56" s="49" t="s">
-        <v>31</v>
-      </c>
-      <c r="L56" s="67" t="s">
+      <c r="H56" s="70" t="s">
+        <v>346</v>
+      </c>
+      <c r="I56" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="L56" s="60" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="39" thickBot="1">
-      <c r="A57" s="44" t="str">
+      <c r="A57" s="42" t="str">
         <f t="shared" si="2"/>
         <v>127_Ed2_012</v>
       </c>
-      <c r="B57" s="44" t="str">
+      <c r="B57" s="42" t="str">
         <f t="shared" si="1"/>
         <v>127_0056</v>
       </c>
       <c r="C57" s="34" t="s">
         <v>202</v>
       </c>
-      <c r="D57" s="60" t="s">
-        <v>300</v>
-      </c>
-      <c r="E57" s="60" t="s">
-        <v>346</v>
-      </c>
-      <c r="F57" s="57" t="s">
-        <v>301</v>
-      </c>
-      <c r="G57" s="60" t="s">
+      <c r="D57" s="57" t="s">
+        <v>292</v>
+      </c>
+      <c r="E57" s="57" t="s">
+        <v>337</v>
+      </c>
+      <c r="F57" s="55" t="s">
+        <v>293</v>
+      </c>
+      <c r="G57" s="57" t="s">
         <v>198</v>
       </c>
-      <c r="H57" s="43" t="s">
-        <v>302</v>
-      </c>
-      <c r="I57" s="49" t="s">
-        <v>31</v>
-      </c>
-      <c r="J57" s="49" t="s">
+      <c r="H57" s="70" t="s">
+        <v>294</v>
+      </c>
+      <c r="I57" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="J57" s="47" t="s">
         <v>195</v>
       </c>
-      <c r="L57" s="67" t="s">
+      <c r="L57" s="60" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="39" thickBot="1">
-      <c r="A58" s="44" t="str">
+      <c r="A58" s="42" t="str">
         <f t="shared" si="2"/>
         <v>127_Ed2_013</v>
       </c>
-      <c r="B58" s="44" t="str">
+      <c r="B58" s="42" t="str">
         <f t="shared" si="1"/>
         <v>127_0057</v>
       </c>
-      <c r="C58" s="47" t="s">
+      <c r="C58" s="45" t="s">
         <v>202</v>
       </c>
-      <c r="D58" s="45" t="s">
+      <c r="D58" s="43" t="s">
+        <v>249</v>
+      </c>
+      <c r="E58" s="43" t="s">
+        <v>250</v>
+      </c>
+      <c r="F58" s="43" t="s">
+        <v>251</v>
+      </c>
+      <c r="G58" s="44" t="s">
+        <v>197</v>
+      </c>
+      <c r="H58" s="69" t="s">
         <v>252</v>
       </c>
-      <c r="E58" s="45" t="s">
-        <v>253</v>
-      </c>
-      <c r="F58" s="45" t="s">
-        <v>254</v>
-      </c>
-      <c r="G58" s="46" t="s">
-        <v>197</v>
-      </c>
-      <c r="H58" s="47" t="s">
-        <v>255</v>
-      </c>
-      <c r="I58" s="49" t="s">
+      <c r="I58" s="47" t="s">
         <v>195</v>
       </c>
-      <c r="L58" s="45" t="s">
+      <c r="L58" s="43" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="26.25" thickBot="1">
-      <c r="A59" s="44" t="str">
+      <c r="A59" s="42" t="str">
         <f t="shared" si="2"/>
         <v>127_Ed2_014</v>
       </c>
-      <c r="B59" s="44" t="str">
+      <c r="B59" s="42" t="str">
         <f t="shared" si="1"/>
         <v>127_0058</v>
       </c>
-      <c r="C59" s="47" t="s">
+      <c r="C59" s="45" t="s">
         <v>200</v>
       </c>
-      <c r="D59" s="45" t="s">
-        <v>256</v>
-      </c>
-      <c r="E59" s="45" t="s">
-        <v>257</v>
-      </c>
-      <c r="F59" s="45" t="s">
-        <v>258</v>
-      </c>
-      <c r="G59" s="46" t="s">
+      <c r="D59" s="43" t="s">
+        <v>253</v>
+      </c>
+      <c r="E59" s="43" t="s">
+        <v>254</v>
+      </c>
+      <c r="F59" s="43" t="s">
+        <v>255</v>
+      </c>
+      <c r="G59" s="44" t="s">
         <v>197</v>
       </c>
-      <c r="H59" s="47">
+      <c r="H59" s="69">
         <v>7.3</v>
       </c>
-      <c r="I59" s="49" t="s">
+      <c r="I59" s="47" t="s">
         <v>195</v>
       </c>
-      <c r="L59" s="45" t="s">
+      <c r="L59" s="43" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="26.25" thickBot="1">
-      <c r="A60" s="44" t="str">
+      <c r="A60" s="42" t="str">
         <f t="shared" si="2"/>
         <v>127_Ed2_015</v>
       </c>
-      <c r="B60" s="44" t="str">
+      <c r="B60" s="42" t="str">
         <f t="shared" si="1"/>
         <v>127_0059</v>
       </c>
-      <c r="C60" s="47" t="s">
+      <c r="C60" s="45" t="s">
         <v>200</v>
       </c>
-      <c r="D60" s="45" t="s">
-        <v>308</v>
-      </c>
-      <c r="E60" s="45" t="s">
-        <v>259</v>
-      </c>
-      <c r="F60" s="45" t="s">
-        <v>260</v>
-      </c>
-      <c r="G60" s="46" t="s">
+      <c r="D60" s="43" t="s">
+        <v>300</v>
+      </c>
+      <c r="E60" s="43" t="s">
+        <v>256</v>
+      </c>
+      <c r="F60" s="43" t="s">
+        <v>257</v>
+      </c>
+      <c r="G60" s="44" t="s">
         <v>198</v>
       </c>
-      <c r="H60" s="47" t="s">
-        <v>261</v>
-      </c>
-      <c r="I60" s="49" t="s">
+      <c r="H60" s="69" t="s">
+        <v>258</v>
+      </c>
+      <c r="I60" s="47" t="s">
         <v>195</v>
       </c>
-      <c r="L60" s="45" t="s">
-        <v>248</v>
+      <c r="L60" s="43" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="61" spans="1:12" ht="26.25" thickBot="1">
-      <c r="A61" s="44" t="str">
+      <c r="A61" s="42" t="str">
         <f t="shared" si="2"/>
         <v>127_Ed2_016</v>
       </c>
-      <c r="B61" s="44" t="str">
+      <c r="B61" s="42" t="str">
         <f t="shared" si="1"/>
         <v>127_0060</v>
       </c>
-      <c r="C61" s="47" t="s">
+      <c r="C61" s="45" t="s">
         <v>202</v>
       </c>
-      <c r="D61" s="45" t="s">
-        <v>262</v>
-      </c>
-      <c r="E61" s="45" t="s">
-        <v>263</v>
-      </c>
-      <c r="F61" s="45" t="s">
-        <v>264</v>
-      </c>
-      <c r="G61" s="46" t="s">
+      <c r="D61" s="43" t="s">
+        <v>259</v>
+      </c>
+      <c r="E61" s="43" t="s">
+        <v>260</v>
+      </c>
+      <c r="F61" s="43" t="s">
+        <v>261</v>
+      </c>
+      <c r="G61" s="44" t="s">
         <v>198</v>
       </c>
-      <c r="H61" s="47" t="s">
-        <v>261</v>
-      </c>
-      <c r="I61" s="49" t="s">
+      <c r="H61" s="69" t="s">
+        <v>258</v>
+      </c>
+      <c r="I61" s="47" t="s">
         <v>195</v>
       </c>
-      <c r="L61" s="45" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" ht="26.25" thickBot="1">
-      <c r="A62" s="44" t="str">
+      <c r="L61" s="43" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="39" thickBot="1">
+      <c r="A62" s="42" t="str">
         <f t="shared" si="2"/>
         <v>127_Ed2_017</v>
       </c>
-      <c r="B62" s="44" t="str">
+      <c r="B62" s="42" t="str">
         <f t="shared" si="1"/>
         <v>127_0061</v>
       </c>
-      <c r="C62" s="47" t="s">
+      <c r="C62" s="45" t="s">
         <v>202</v>
       </c>
-      <c r="D62" s="45" t="s">
-        <v>265</v>
-      </c>
-      <c r="E62" s="45" t="s">
-        <v>266</v>
-      </c>
-      <c r="F62" s="45" t="s">
-        <v>267</v>
-      </c>
-      <c r="G62" s="46" t="s">
-        <v>198</v>
-      </c>
-      <c r="H62" s="47" t="s">
-        <v>234</v>
-      </c>
-      <c r="I62" s="49" t="s">
+      <c r="D62" s="43" t="s">
+        <v>262</v>
+      </c>
+      <c r="E62" s="43" t="s">
+        <v>263</v>
+      </c>
+      <c r="F62" s="43" t="s">
+        <v>264</v>
+      </c>
+      <c r="G62" s="44" t="s">
+        <v>209</v>
+      </c>
+      <c r="I62" s="47" t="s">
         <v>195</v>
       </c>
-      <c r="L62" s="45" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" ht="39" thickBot="1">
-      <c r="A63" s="44" t="str">
+      <c r="L62" s="43" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="26.25" thickBot="1">
+      <c r="A63" s="42" t="str">
         <f t="shared" si="2"/>
         <v>127_Ed2_018</v>
       </c>
-      <c r="B63" s="44" t="str">
+      <c r="B63" s="42" t="str">
         <f t="shared" si="1"/>
         <v>127_0062</v>
       </c>
-      <c r="C63" s="47" t="s">
+      <c r="C63" s="45" t="s">
         <v>202</v>
       </c>
-      <c r="D63" s="45" t="s">
-        <v>268</v>
-      </c>
-      <c r="E63" s="45" t="s">
-        <v>269</v>
-      </c>
-      <c r="F63" s="45" t="s">
-        <v>270</v>
-      </c>
-      <c r="G63" s="46" t="s">
-        <v>209</v>
-      </c>
-      <c r="I63" s="49" t="s">
+      <c r="D63" s="43" t="s">
+        <v>301</v>
+      </c>
+      <c r="E63" s="43" t="s">
+        <v>302</v>
+      </c>
+      <c r="F63" s="43" t="s">
+        <v>303</v>
+      </c>
+      <c r="G63" s="44" t="s">
+        <v>198</v>
+      </c>
+      <c r="H63" s="69" t="s">
+        <v>347</v>
+      </c>
+      <c r="I63" s="47" t="s">
         <v>195</v>
       </c>
-      <c r="L63" s="45" t="s">
-        <v>274</v>
+      <c r="L63" s="43" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="26.25" thickBot="1">
-      <c r="A64" s="44" t="str">
+      <c r="A64" s="42" t="str">
         <f t="shared" si="2"/>
         <v>127_Ed2_019</v>
       </c>
-      <c r="B64" s="44" t="str">
+      <c r="B64" s="42" t="str">
         <f t="shared" si="1"/>
         <v>127_0063</v>
       </c>
-      <c r="C64" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="D64" s="45" t="s">
-        <v>309</v>
-      </c>
-      <c r="E64" s="45" t="s">
-        <v>310</v>
-      </c>
-      <c r="F64" s="45" t="s">
-        <v>311</v>
-      </c>
-      <c r="G64" s="46" t="s">
+      <c r="C64" s="49" t="s">
+        <v>200</v>
+      </c>
+      <c r="D64" s="61" t="s">
+        <v>304</v>
+      </c>
+      <c r="E64" s="57" t="s">
+        <v>348</v>
+      </c>
+      <c r="F64" s="55" t="s">
+        <v>305</v>
+      </c>
+      <c r="G64" s="57" t="s">
         <v>198</v>
       </c>
-      <c r="H64" s="47" t="s">
-        <v>255</v>
-      </c>
-      <c r="I64" s="49" t="s">
+      <c r="H64" s="71" t="s">
+        <v>349</v>
+      </c>
+      <c r="I64" s="47" t="s">
         <v>195</v>
       </c>
-      <c r="L64" s="45" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" ht="26.25" thickBot="1">
-      <c r="A65" s="44" t="str">
+      <c r="L64" s="60" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="30.75" thickBot="1">
+      <c r="A65" s="42" t="str">
         <f t="shared" si="2"/>
         <v>127_Ed2_020</v>
       </c>
-      <c r="B65" s="44" t="str">
+      <c r="B65" s="42" t="str">
         <f t="shared" si="1"/>
         <v>127_0064</v>
       </c>
-      <c r="C65" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="D65" s="68" t="s">
-        <v>312</v>
-      </c>
-      <c r="E65" s="60" t="s">
-        <v>313</v>
-      </c>
-      <c r="F65" s="57" t="s">
-        <v>314</v>
-      </c>
-      <c r="G65" s="60" t="s">
+      <c r="C65" s="49" t="s">
+        <v>202</v>
+      </c>
+      <c r="D65" s="62" t="s">
+        <v>306</v>
+      </c>
+      <c r="E65" s="46" t="s">
+        <v>307</v>
+      </c>
+      <c r="F65" s="43" t="s">
+        <v>308</v>
+      </c>
+      <c r="G65" s="52" t="s">
         <v>198</v>
       </c>
-      <c r="H65" s="59">
-        <v>2.4</v>
-      </c>
-      <c r="I65" s="49" t="s">
+      <c r="H65" s="69" t="s">
+        <v>309</v>
+      </c>
+      <c r="I65" s="47" t="s">
         <v>195</v>
       </c>
-      <c r="L65" s="67" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" ht="30.75" thickBot="1">
-      <c r="A66" s="44" t="str">
+      <c r="L65" s="43" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="51.75" thickBot="1">
+      <c r="A66" s="42" t="str">
         <f t="shared" si="2"/>
         <v>127_Ed2_021</v>
       </c>
-      <c r="B66" s="44" t="str">
+      <c r="B66" s="42" t="str">
         <f t="shared" si="1"/>
         <v>127_0065</v>
       </c>
-      <c r="C66" s="51" t="s">
+      <c r="C66" s="49" t="s">
         <v>202</v>
       </c>
-      <c r="D66" s="69" t="s">
-        <v>315</v>
-      </c>
-      <c r="E66" s="48" t="s">
-        <v>316</v>
-      </c>
-      <c r="F66" s="45" t="s">
-        <v>317</v>
-      </c>
-      <c r="G66" s="54" t="s">
+      <c r="D66" s="43" t="s">
+        <v>310</v>
+      </c>
+      <c r="E66" s="46" t="s">
+        <v>312</v>
+      </c>
+      <c r="F66" s="43" t="s">
+        <v>311</v>
+      </c>
+      <c r="G66" s="52" t="s">
         <v>198</v>
       </c>
-      <c r="H66" s="47" t="s">
-        <v>318</v>
-      </c>
-      <c r="I66" s="49" t="s">
+      <c r="H66" s="69" t="s">
+        <v>309</v>
+      </c>
+      <c r="I66" s="47" t="s">
         <v>195</v>
       </c>
-      <c r="L66" s="45" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" ht="51.75" thickBot="1">
-      <c r="A67" s="44" t="str">
+      <c r="L66" s="43" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="39" thickBot="1">
+      <c r="A67" s="42" t="str">
         <f t="shared" si="2"/>
         <v>127_Ed2_022</v>
       </c>
-      <c r="B67" s="44" t="str">
+      <c r="B67" s="42" t="str">
         <f t="shared" si="1"/>
         <v>127_0066</v>
       </c>
-      <c r="C67" s="51" t="s">
+      <c r="C67" s="49" t="s">
         <v>202</v>
       </c>
-      <c r="D67" s="45" t="s">
-        <v>319</v>
-      </c>
-      <c r="E67" s="48" t="s">
-        <v>321</v>
-      </c>
-      <c r="F67" s="45" t="s">
-        <v>320</v>
-      </c>
-      <c r="G67" s="54" t="s">
+      <c r="D67" s="43" t="s">
+        <v>316</v>
+      </c>
+      <c r="E67" s="46" t="s">
+        <v>313</v>
+      </c>
+      <c r="F67" s="43" t="s">
+        <v>314</v>
+      </c>
+      <c r="G67" s="52" t="s">
         <v>198</v>
       </c>
-      <c r="H67" s="47" t="s">
-        <v>318</v>
-      </c>
-      <c r="I67" s="49" t="s">
+      <c r="H67" s="69" t="s">
+        <v>315</v>
+      </c>
+      <c r="I67" s="47" t="s">
         <v>195</v>
       </c>
-      <c r="L67" s="45" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" ht="39" thickBot="1">
-      <c r="A68" s="44" t="str">
+    </row>
+    <row r="68" spans="1:13" ht="26.25" thickBot="1">
+      <c r="A68" s="42" t="str">
         <f t="shared" si="2"/>
         <v>127_Ed2_023</v>
       </c>
-      <c r="B68" s="44" t="str">
+      <c r="B68" s="42" t="str">
         <f t="shared" si="1"/>
         <v>127_0067</v>
       </c>
-      <c r="C68" s="51" t="s">
-        <v>202</v>
-      </c>
-      <c r="D68" s="45" t="s">
-        <v>325</v>
-      </c>
-      <c r="E68" s="48" t="s">
-        <v>322</v>
-      </c>
-      <c r="F68" s="45" t="s">
-        <v>323</v>
-      </c>
-      <c r="G68" s="54" t="s">
-        <v>198</v>
-      </c>
-      <c r="H68" s="47" t="s">
-        <v>324</v>
-      </c>
-      <c r="I68" s="49" t="s">
+      <c r="C68" s="45" t="s">
+        <v>200</v>
+      </c>
+      <c r="D68" s="43" t="s">
+        <v>317</v>
+      </c>
+      <c r="E68" s="43" t="s">
+        <v>318</v>
+      </c>
+      <c r="F68" s="43" t="s">
+        <v>319</v>
+      </c>
+      <c r="G68" s="44" t="s">
+        <v>209</v>
+      </c>
+      <c r="I68" s="47" t="s">
         <v>195</v>
       </c>
+      <c r="L68" s="43" t="s">
+        <v>320</v>
+      </c>
     </row>
     <row r="69" spans="1:13" ht="26.25" thickBot="1">
-      <c r="A69" s="44" t="str">
+      <c r="A69" s="42" t="str">
         <f t="shared" si="2"/>
         <v>127_Ed2_024</v>
       </c>
-      <c r="B69" s="44" t="str">
+      <c r="B69" s="42" t="str">
         <f t="shared" si="1"/>
         <v>127_0068</v>
       </c>
-      <c r="C69" s="47" t="s">
-        <v>200</v>
-      </c>
-      <c r="D69" s="45" t="s">
-        <v>326</v>
-      </c>
-      <c r="E69" s="45" t="s">
-        <v>327</v>
-      </c>
-      <c r="F69" s="45" t="s">
-        <v>328</v>
-      </c>
-      <c r="G69" s="46" t="s">
+      <c r="C69" s="45" t="s">
+        <v>202</v>
+      </c>
+      <c r="D69" s="43" t="s">
+        <v>321</v>
+      </c>
+      <c r="E69" s="43" t="s">
+        <v>322</v>
+      </c>
+      <c r="F69" s="43" t="s">
+        <v>323</v>
+      </c>
+      <c r="G69" s="44" t="s">
         <v>209</v>
       </c>
-      <c r="I69" s="49" t="s">
+      <c r="I69" s="47" t="s">
         <v>195</v>
       </c>
-      <c r="L69" s="45" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" ht="26.25" thickBot="1">
-      <c r="A70" s="44" t="str">
-        <f t="shared" si="2"/>
-        <v>127_Ed2_025</v>
-      </c>
-      <c r="B70" s="44" t="str">
-        <f t="shared" si="1"/>
-        <v>127_0069</v>
-      </c>
-      <c r="C70" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="D70" s="45" t="s">
-        <v>330</v>
-      </c>
-      <c r="E70" s="45" t="s">
-        <v>331</v>
-      </c>
-      <c r="F70" s="45" t="s">
-        <v>332</v>
-      </c>
-      <c r="G70" s="46" t="s">
-        <v>209</v>
-      </c>
-      <c r="I70" s="49" t="s">
-        <v>195</v>
-      </c>
-      <c r="L70" s="45" t="s">
-        <v>248</v>
-      </c>
-      <c r="M70" s="45" t="s">
-        <v>347</v>
-      </c>
+      <c r="L69" s="43" t="s">
+        <v>245</v>
+      </c>
+      <c r="M69" s="43" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" thickBot="1">
+      <c r="C70" s="49"/>
+      <c r="E70" s="46"/>
     </row>
     <row r="71" spans="1:13" thickBot="1">
-      <c r="C71" s="51"/>
-      <c r="E71" s="48"/>
+      <c r="C71" s="49"/>
+      <c r="E71" s="46"/>
     </row>
     <row r="72" spans="1:13" thickBot="1">
-      <c r="C72" s="51"/>
-      <c r="E72" s="48"/>
+      <c r="C72" s="49"/>
+      <c r="E72" s="46"/>
     </row>
     <row r="73" spans="1:13" thickBot="1">
-      <c r="C73" s="51"/>
-      <c r="E73" s="48"/>
+      <c r="C73" s="49"/>
+      <c r="E73" s="46"/>
     </row>
     <row r="74" spans="1:13" thickBot="1">
-      <c r="C74" s="51"/>
-      <c r="E74" s="48"/>
+      <c r="C74" s="49"/>
+      <c r="E74" s="46"/>
     </row>
     <row r="75" spans="1:13" thickBot="1">
-      <c r="C75" s="51"/>
-      <c r="E75" s="48"/>
+      <c r="C75" s="49"/>
+      <c r="E75" s="46"/>
     </row>
     <row r="76" spans="1:13" thickBot="1">
-      <c r="C76" s="51"/>
-      <c r="E76" s="48"/>
+      <c r="C76" s="49"/>
+      <c r="E76" s="46"/>
     </row>
     <row r="77" spans="1:13" thickBot="1">
-      <c r="C77" s="51"/>
-      <c r="E77" s="48"/>
+      <c r="C77" s="49"/>
+      <c r="E77" s="46"/>
     </row>
     <row r="78" spans="1:13" thickBot="1">
-      <c r="C78" s="51"/>
-      <c r="E78" s="48"/>
+      <c r="C78" s="49"/>
+      <c r="E78" s="46"/>
     </row>
     <row r="79" spans="1:13" thickBot="1">
-      <c r="C79" s="51"/>
-      <c r="E79" s="48"/>
+      <c r="C79" s="49"/>
+      <c r="E79" s="46"/>
     </row>
     <row r="80" spans="1:13" thickBot="1">
-      <c r="C80" s="51"/>
-      <c r="E80" s="48"/>
+      <c r="C80" s="49"/>
+      <c r="E80" s="46"/>
     </row>
     <row r="81" spans="3:5" thickBot="1">
-      <c r="C81" s="51"/>
-      <c r="E81" s="48"/>
+      <c r="C81" s="49"/>
+      <c r="E81" s="46"/>
     </row>
     <row r="82" spans="3:5" thickBot="1">
-      <c r="C82" s="51"/>
-      <c r="E82" s="48"/>
+      <c r="C82" s="49"/>
+      <c r="E82" s="46"/>
     </row>
     <row r="83" spans="3:5" thickBot="1">
-      <c r="C83" s="51"/>
-      <c r="E83" s="48"/>
+      <c r="C83" s="49"/>
+      <c r="E83" s="46"/>
     </row>
     <row r="84" spans="3:5" thickBot="1">
-      <c r="C84" s="51"/>
-      <c r="E84" s="48"/>
+      <c r="C84" s="49"/>
+      <c r="E84" s="46"/>
     </row>
     <row r="85" spans="3:5" thickBot="1">
-      <c r="C85" s="51"/>
-      <c r="E85" s="48"/>
+      <c r="C85" s="49"/>
+      <c r="E85" s="46"/>
     </row>
     <row r="86" spans="3:5" thickBot="1">
-      <c r="C86" s="51"/>
-      <c r="E86" s="48"/>
+      <c r="C86" s="49"/>
+      <c r="E86" s="46"/>
     </row>
     <row r="87" spans="3:5" thickBot="1">
-      <c r="C87" s="51"/>
-      <c r="E87" s="48"/>
+      <c r="C87" s="49"/>
+      <c r="E87" s="46"/>
     </row>
     <row r="88" spans="3:5" thickBot="1">
-      <c r="C88" s="51"/>
-      <c r="E88" s="48"/>
+      <c r="C88" s="49"/>
+      <c r="E88" s="46"/>
     </row>
     <row r="89" spans="3:5" thickBot="1">
-      <c r="C89" s="51"/>
-      <c r="E89" s="48"/>
+      <c r="C89" s="49"/>
+      <c r="E89" s="46"/>
     </row>
     <row r="90" spans="3:5" thickBot="1">
-      <c r="C90" s="51"/>
-      <c r="E90" s="48"/>
+      <c r="C90" s="49"/>
+      <c r="E90" s="46"/>
     </row>
     <row r="91" spans="3:5" thickBot="1">
-      <c r="C91" s="51"/>
-      <c r="E91" s="48"/>
+      <c r="C91" s="49"/>
+      <c r="E91" s="46"/>
     </row>
     <row r="92" spans="3:5" thickBot="1">
-      <c r="C92" s="51"/>
-      <c r="E92" s="48"/>
+      <c r="C92" s="49"/>
+      <c r="E92" s="46"/>
     </row>
     <row r="93" spans="3:5" thickBot="1">
-      <c r="C93" s="51"/>
-      <c r="E93" s="48"/>
+      <c r="C93" s="49"/>
+      <c r="E93" s="46"/>
     </row>
     <row r="94" spans="3:5" thickBot="1">
-      <c r="C94" s="51"/>
-      <c r="E94" s="48"/>
+      <c r="C94" s="49"/>
+      <c r="E94" s="46"/>
     </row>
     <row r="95" spans="3:5" thickBot="1">
-      <c r="C95" s="51"/>
-      <c r="E95" s="48"/>
+      <c r="C95" s="49"/>
+      <c r="E95" s="46"/>
     </row>
     <row r="96" spans="3:5" thickBot="1">
-      <c r="C96" s="51"/>
-      <c r="E96" s="48"/>
+      <c r="C96" s="49"/>
+      <c r="E96" s="46"/>
     </row>
     <row r="97" spans="3:5" thickBot="1">
-      <c r="C97" s="51"/>
-      <c r="E97" s="48"/>
+      <c r="C97" s="49"/>
+      <c r="E97" s="46"/>
     </row>
     <row r="98" spans="3:5" thickBot="1">
-      <c r="C98" s="51"/>
-      <c r="E98" s="48"/>
+      <c r="C98" s="49"/>
+      <c r="E98" s="46"/>
     </row>
     <row r="99" spans="3:5" thickBot="1">
-      <c r="C99" s="51"/>
-      <c r="E99" s="48"/>
+      <c r="C99" s="49"/>
+      <c r="E99" s="46"/>
     </row>
     <row r="100" spans="3:5" thickBot="1">
-      <c r="C100" s="51"/>
-      <c r="E100" s="48"/>
+      <c r="C100" s="49"/>
+      <c r="E100" s="46"/>
     </row>
     <row r="101" spans="3:5" thickBot="1">
-      <c r="C101" s="51"/>
-      <c r="E101" s="48"/>
+      <c r="C101" s="49"/>
+      <c r="E101" s="46"/>
     </row>
     <row r="102" spans="3:5" thickBot="1">
-      <c r="C102" s="51"/>
-      <c r="E102" s="48"/>
+      <c r="C102" s="49"/>
+      <c r="E102" s="46"/>
     </row>
     <row r="103" spans="3:5" thickBot="1">
-      <c r="C103" s="51"/>
-      <c r="E103" s="48"/>
+      <c r="C103" s="49"/>
+      <c r="E103" s="46"/>
     </row>
     <row r="104" spans="3:5" thickBot="1">
-      <c r="C104" s="51"/>
-      <c r="E104" s="48"/>
+      <c r="C104" s="49"/>
+      <c r="E104" s="46"/>
     </row>
     <row r="105" spans="3:5" thickBot="1">
-      <c r="C105" s="51"/>
-      <c r="E105" s="48"/>
+      <c r="C105" s="49"/>
+      <c r="E105" s="46"/>
     </row>
     <row r="106" spans="3:5" thickBot="1">
-      <c r="C106" s="51"/>
-      <c r="E106" s="48"/>
+      <c r="C106" s="49"/>
+      <c r="E106" s="46"/>
     </row>
     <row r="107" spans="3:5" thickBot="1">
-      <c r="C107" s="51"/>
-      <c r="E107" s="48"/>
+      <c r="C107" s="49"/>
+      <c r="E107" s="46"/>
     </row>
     <row r="108" spans="3:5" thickBot="1">
-      <c r="C108" s="51"/>
-      <c r="E108" s="48"/>
+      <c r="C108" s="49"/>
+      <c r="E108" s="46"/>
     </row>
     <row r="109" spans="3:5" thickBot="1">
-      <c r="C109" s="51"/>
-      <c r="E109" s="48"/>
-    </row>
-    <row r="110" spans="3:5" thickBot="1">
-      <c r="C110" s="51"/>
-      <c r="E110" s="48"/>
-    </row>
+      <c r="C109" s="49"/>
+      <c r="E109" s="46"/>
+    </row>
+    <row r="110" spans="3:5" ht="12.75"/>
     <row r="111" spans="3:5" ht="12.75"/>
     <row r="112" spans="3:5" ht="12.75"/>
     <row r="113" ht="12.75"/>
@@ -4780,11 +4761,11 @@
     <row r="135" ht="12.75"/>
     <row r="136" ht="12.75"/>
     <row r="137" ht="12.75"/>
-    <row r="138" ht="12.75"/>
+    <row r="138"/>
   </sheetData>
-  <autoFilter ref="K1:K113" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="K1:K112" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C110" xr:uid="{1FB138CC-14EF-4406-9E7B-EC5039F9ECE1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C109" xr:uid="{1FB138CC-14EF-4406-9E7B-EC5039F9ECE1}">
       <formula1>"C,E,W"</formula1>
     </dataValidation>
   </dataValidations>

--- a/S158_127/1.0.0/S-158_127_1_0_0_20260323.xlsx
+++ b/S158_127/1.0.0/S-158_127_1_0_0_20260323.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\work\git\S-127-Product-Specification-Development\S158_127\1.0.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A30E0CA-5B83-4DD0-96F2-7A2571AABB92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A4878A-B860-4638-ADC6-76B2CC19EAC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="28110" windowHeight="18240" tabRatio="647" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="350">
   <si>
     <t>Document Number</t>
   </si>
@@ -1636,6 +1636,21 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="8" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1647,21 +1662,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1971,14 +1971,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="33.6" customHeight="1">
-      <c r="B2" s="63" t="s">
+      <c r="B2" s="68" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="65"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="70"/>
       <c r="H2" s="25"/>
     </row>
     <row r="3" spans="2:8" s="1" customFormat="1" ht="20.45" customHeight="1">
@@ -2104,7 +2104,7 @@
       <c r="G12" s="26"/>
     </row>
     <row r="13" spans="2:8" s="1" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B13" s="66" t="s">
+      <c r="B13" s="71" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="5" t="s">
@@ -2118,7 +2118,7 @@
       <c r="G13" s="26"/>
     </row>
     <row r="14" spans="2:8" s="1" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B14" s="66"/>
+      <c r="B14" s="71"/>
       <c r="C14" s="15" t="s">
         <v>34</v>
       </c>
@@ -2130,7 +2130,7 @@
       <c r="G14" s="26"/>
     </row>
     <row r="15" spans="2:8" s="1" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B15" s="66"/>
+      <c r="B15" s="71"/>
       <c r="C15" s="16" t="s">
         <v>35</v>
       </c>
@@ -2142,7 +2142,7 @@
       <c r="G15" s="26"/>
     </row>
     <row r="16" spans="2:8" s="1" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B16" s="66"/>
+      <c r="B16" s="71"/>
       <c r="C16" s="37" t="s">
         <v>27</v>
       </c>
@@ -2154,7 +2154,7 @@
       <c r="G16" s="26"/>
     </row>
     <row r="17" spans="2:7" s="1" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B17" s="66"/>
+      <c r="B17" s="71"/>
       <c r="C17" s="17"/>
       <c r="D17" s="18"/>
       <c r="E17" s="18"/>
@@ -2162,7 +2162,7 @@
       <c r="G17" s="26"/>
     </row>
     <row r="18" spans="2:7" s="1" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B18" s="66"/>
+      <c r="B18" s="71"/>
       <c r="C18" s="19"/>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
@@ -2207,7 +2207,7 @@
     <col min="5" max="5" width="58.85546875" style="43" customWidth="1"/>
     <col min="6" max="6" width="34.7109375" style="43" customWidth="1"/>
     <col min="7" max="7" width="18.140625" style="52" customWidth="1"/>
-    <col min="8" max="8" width="16.28515625" style="69" customWidth="1"/>
+    <col min="8" max="8" width="16.28515625" style="65" customWidth="1"/>
     <col min="9" max="9" width="10.42578125" style="47" customWidth="1"/>
     <col min="10" max="10" width="8.28515625" style="47" customWidth="1"/>
     <col min="11" max="11" width="8" style="47" customWidth="1"/>
@@ -2238,7 +2238,7 @@
       <c r="G1" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="67" t="s">
+      <c r="H1" s="63" t="s">
         <v>21</v>
       </c>
       <c r="I1" s="59" t="s">
@@ -2280,7 +2280,7 @@
       <c r="G2" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="H2" s="68">
+      <c r="H2" s="64">
         <v>7.3</v>
       </c>
       <c r="I2" s="43" t="s">
@@ -2313,7 +2313,7 @@
       <c r="G3" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="H3" s="68">
+      <c r="H3" s="64">
         <v>12.8</v>
       </c>
       <c r="I3" s="43" t="s">
@@ -2346,7 +2346,7 @@
       <c r="G4" s="48" t="s">
         <v>198</v>
       </c>
-      <c r="H4" s="68">
+      <c r="H4" s="64">
         <v>4.2</v>
       </c>
       <c r="I4" s="43" t="s">
@@ -2379,7 +2379,7 @@
       <c r="G5" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="H5" s="68">
+      <c r="H5" s="64">
         <v>12.4</v>
       </c>
       <c r="I5" s="43" t="s">
@@ -2414,7 +2414,7 @@
       <c r="G6" s="48" t="s">
         <v>199</v>
       </c>
-      <c r="H6" s="68" t="s">
+      <c r="H6" s="64" t="s">
         <v>203</v>
       </c>
       <c r="I6" s="43" t="s">
@@ -2449,7 +2449,7 @@
       <c r="G7" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="H7" s="68">
+      <c r="H7" s="64">
         <v>12.5</v>
       </c>
       <c r="I7" s="43" t="s">
@@ -2489,7 +2489,7 @@
       <c r="G8" s="53" t="s">
         <v>198</v>
       </c>
-      <c r="H8" s="68" t="s">
+      <c r="H8" s="64" t="s">
         <v>208</v>
       </c>
       <c r="I8" s="43" t="s">
@@ -2529,7 +2529,7 @@
       <c r="G9" s="53" t="s">
         <v>209</v>
       </c>
-      <c r="H9" s="68"/>
+      <c r="H9" s="64"/>
       <c r="I9" s="43" t="s">
         <v>31</v>
       </c>
@@ -2566,7 +2566,7 @@
       <c r="G10" s="53" t="s">
         <v>209</v>
       </c>
-      <c r="H10" s="68"/>
+      <c r="H10" s="64"/>
       <c r="I10" s="43" t="s">
         <v>31</v>
       </c>
@@ -2597,7 +2597,7 @@
       <c r="G11" s="53" t="s">
         <v>197</v>
       </c>
-      <c r="H11" s="68">
+      <c r="H11" s="64">
         <v>3</v>
       </c>
       <c r="I11" s="43" t="s">
@@ -2630,7 +2630,7 @@
       <c r="G12" s="53" t="s">
         <v>197</v>
       </c>
-      <c r="H12" s="68">
+      <c r="H12" s="64">
         <v>3</v>
       </c>
       <c r="I12" s="43" t="s">
@@ -2663,7 +2663,7 @@
       <c r="G13" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="H13" s="68" t="s">
+      <c r="H13" s="64" t="s">
         <v>265</v>
       </c>
       <c r="I13" s="43" t="s">
@@ -2699,7 +2699,7 @@
       <c r="G14" s="53" t="s">
         <v>199</v>
       </c>
-      <c r="H14" s="68" t="s">
+      <c r="H14" s="64" t="s">
         <v>228</v>
       </c>
       <c r="I14" s="43" t="s">
@@ -2732,7 +2732,7 @@
       <c r="G15" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="H15" s="68">
+      <c r="H15" s="64">
         <v>12.9</v>
       </c>
       <c r="I15" s="43" t="s">
@@ -2765,7 +2765,7 @@
       <c r="G16" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="H16" s="68" t="s">
+      <c r="H16" s="64" t="s">
         <v>339</v>
       </c>
       <c r="I16" s="43" t="s">
@@ -2804,7 +2804,7 @@
       <c r="G17" s="48" t="s">
         <v>198</v>
       </c>
-      <c r="H17" s="68" t="s">
+      <c r="H17" s="64" t="s">
         <v>229</v>
       </c>
       <c r="I17" s="43" t="s">
@@ -2840,7 +2840,7 @@
       <c r="G18" s="52" t="s">
         <v>197</v>
       </c>
-      <c r="H18" s="69" t="s">
+      <c r="H18" s="65" t="s">
         <v>230</v>
       </c>
       <c r="I18" s="43" t="s">
@@ -2876,7 +2876,7 @@
       <c r="G19" s="53" t="s">
         <v>198</v>
       </c>
-      <c r="H19" s="69" t="s">
+      <c r="H19" s="65" t="s">
         <v>266</v>
       </c>
       <c r="I19" s="43" t="s">
@@ -2909,7 +2909,7 @@
       <c r="G20" s="52" t="s">
         <v>198</v>
       </c>
-      <c r="H20" s="69" t="s">
+      <c r="H20" s="65" t="s">
         <v>234</v>
       </c>
       <c r="I20" s="43" t="s">
@@ -2942,7 +2942,7 @@
       <c r="G21" s="53" t="s">
         <v>197</v>
       </c>
-      <c r="H21" s="68">
+      <c r="H21" s="64">
         <v>13.1</v>
       </c>
       <c r="I21" s="43" t="s">
@@ -2975,7 +2975,7 @@
       <c r="G22" s="52" t="s">
         <v>197</v>
       </c>
-      <c r="H22" s="69">
+      <c r="H22" s="65">
         <v>13.1</v>
       </c>
       <c r="I22" s="43" t="s">
@@ -3008,7 +3008,7 @@
       <c r="G23" s="52" t="s">
         <v>197</v>
       </c>
-      <c r="H23" s="69">
+      <c r="H23" s="65">
         <v>14.1</v>
       </c>
       <c r="I23" s="43" t="s">
@@ -3047,7 +3047,7 @@
       <c r="G24" s="53" t="s">
         <v>199</v>
       </c>
-      <c r="H24" s="68" t="s">
+      <c r="H24" s="64" t="s">
         <v>231</v>
       </c>
       <c r="I24" s="43" t="s">
@@ -3080,7 +3080,7 @@
       <c r="G25" s="52" t="s">
         <v>198</v>
       </c>
-      <c r="H25" s="69" t="s">
+      <c r="H25" s="65" t="s">
         <v>229</v>
       </c>
       <c r="I25" s="43" t="s">
@@ -3113,7 +3113,7 @@
       <c r="G26" s="53" t="s">
         <v>199</v>
       </c>
-      <c r="H26" s="68" t="s">
+      <c r="H26" s="64" t="s">
         <v>340</v>
       </c>
       <c r="I26" s="43" t="s">
@@ -3176,7 +3176,7 @@
       <c r="G28" s="53" t="s">
         <v>198</v>
       </c>
-      <c r="H28" s="68" t="s">
+      <c r="H28" s="64" t="s">
         <v>341</v>
       </c>
       <c r="I28" s="43" t="s">
@@ -3209,7 +3209,7 @@
       <c r="G29" s="53" t="s">
         <v>198</v>
       </c>
-      <c r="H29" s="69" t="s">
+      <c r="H29" s="65" t="s">
         <v>342</v>
       </c>
       <c r="I29" s="43" t="s">
@@ -3245,7 +3245,7 @@
       <c r="G30" s="53" t="s">
         <v>198</v>
       </c>
-      <c r="H30" s="69" t="s">
+      <c r="H30" s="65" t="s">
         <v>233</v>
       </c>
       <c r="I30" s="43" t="s">
@@ -3281,7 +3281,7 @@
       <c r="G31" s="53" t="s">
         <v>198</v>
       </c>
-      <c r="H31" s="68" t="s">
+      <c r="H31" s="64" t="s">
         <v>343</v>
       </c>
       <c r="I31" s="43" t="s">
@@ -3314,7 +3314,7 @@
       <c r="G32" s="53" t="s">
         <v>198</v>
       </c>
-      <c r="H32" s="69">
+      <c r="H32" s="65">
         <v>13.1</v>
       </c>
       <c r="I32" s="43" t="s">
@@ -3347,7 +3347,7 @@
       <c r="G33" s="53" t="s">
         <v>198</v>
       </c>
-      <c r="H33" s="68" t="s">
+      <c r="H33" s="64" t="s">
         <v>297</v>
       </c>
       <c r="I33" s="43" t="s">
@@ -3380,7 +3380,7 @@
       <c r="G34" s="53" t="s">
         <v>198</v>
       </c>
-      <c r="H34" s="69">
+      <c r="H34" s="65">
         <v>14.6</v>
       </c>
       <c r="I34" s="43" t="s">
@@ -3413,7 +3413,7 @@
       <c r="G35" s="53" t="s">
         <v>199</v>
       </c>
-      <c r="H35" s="69" t="s">
+      <c r="H35" s="65" t="s">
         <v>236</v>
       </c>
       <c r="I35" s="43" t="s">
@@ -3446,7 +3446,7 @@
       <c r="G36" s="52" t="s">
         <v>198</v>
       </c>
-      <c r="H36" s="69" t="s">
+      <c r="H36" s="65" t="s">
         <v>222</v>
       </c>
       <c r="I36" s="43" t="s">
@@ -3482,7 +3482,7 @@
       <c r="G37" s="53" t="s">
         <v>197</v>
       </c>
-      <c r="H37" s="69">
+      <c r="H37" s="65">
         <v>12.11</v>
       </c>
       <c r="I37" s="43" t="s">
@@ -3515,7 +3515,7 @@
       <c r="G38" s="53" t="s">
         <v>197</v>
       </c>
-      <c r="H38" s="68">
+      <c r="H38" s="64">
         <v>7.5</v>
       </c>
       <c r="I38" s="43" t="s">
@@ -3554,7 +3554,7 @@
       <c r="G39" s="52" t="s">
         <v>198</v>
       </c>
-      <c r="H39" s="69" t="s">
+      <c r="H39" s="65" t="s">
         <v>237</v>
       </c>
       <c r="I39" s="43" t="s">
@@ -3587,7 +3587,7 @@
       <c r="G40" s="52" t="s">
         <v>198</v>
       </c>
-      <c r="H40" s="69" t="s">
+      <c r="H40" s="65" t="s">
         <v>238</v>
       </c>
       <c r="I40" s="43" t="s">
@@ -3620,7 +3620,7 @@
       <c r="G41" s="52" t="s">
         <v>198</v>
       </c>
-      <c r="H41" s="69" t="s">
+      <c r="H41" s="65" t="s">
         <v>239</v>
       </c>
       <c r="I41" s="43" t="s">
@@ -3653,7 +3653,7 @@
       <c r="G42" s="52" t="s">
         <v>198</v>
       </c>
-      <c r="H42" s="69" t="s">
+      <c r="H42" s="65" t="s">
         <v>240</v>
       </c>
       <c r="I42" s="43" t="s">
@@ -3686,7 +3686,7 @@
       <c r="G43" s="52" t="s">
         <v>197</v>
       </c>
-      <c r="H43" s="69" t="s">
+      <c r="H43" s="65" t="s">
         <v>240</v>
       </c>
       <c r="I43" s="43" t="s">
@@ -3719,7 +3719,7 @@
       <c r="G44" s="52" t="s">
         <v>198</v>
       </c>
-      <c r="H44" s="69" t="s">
+      <c r="H44" s="65" t="s">
         <v>226</v>
       </c>
       <c r="I44" s="43" t="s">
@@ -3752,7 +3752,7 @@
       <c r="G45" s="52" t="s">
         <v>198</v>
       </c>
-      <c r="H45" s="69" t="s">
+      <c r="H45" s="65" t="s">
         <v>235</v>
       </c>
       <c r="I45" s="43" t="s">
@@ -3786,7 +3786,7 @@
       <c r="G46" s="53" t="s">
         <v>197</v>
       </c>
-      <c r="H46" s="68">
+      <c r="H46" s="64">
         <v>13.1</v>
       </c>
       <c r="I46" s="47" t="s">
@@ -3823,7 +3823,7 @@
       <c r="G47" s="44" t="s">
         <v>198</v>
       </c>
-      <c r="H47" s="69" t="s">
+      <c r="H47" s="65" t="s">
         <v>244</v>
       </c>
       <c r="I47" s="47" t="s">
@@ -3857,7 +3857,7 @@
       <c r="G48" s="53" t="s">
         <v>197</v>
       </c>
-      <c r="H48" s="68">
+      <c r="H48" s="64">
         <v>7.3</v>
       </c>
       <c r="I48" s="47" t="s">
@@ -3891,7 +3891,7 @@
       <c r="G49" s="57" t="s">
         <v>198</v>
       </c>
-      <c r="H49" s="70" t="s">
+      <c r="H49" s="66" t="s">
         <v>344</v>
       </c>
       <c r="I49" s="43" t="s">
@@ -3925,7 +3925,7 @@
       <c r="G50" s="57" t="s">
         <v>198</v>
       </c>
-      <c r="H50" s="70" t="s">
+      <c r="H50" s="66" t="s">
         <v>345</v>
       </c>
       <c r="I50" s="43" t="s">
@@ -3959,7 +3959,7 @@
       <c r="G51" s="57" t="s">
         <v>198</v>
       </c>
-      <c r="H51" s="70" t="s">
+      <c r="H51" s="66" t="s">
         <v>345</v>
       </c>
       <c r="I51" s="43" t="s">
@@ -3993,7 +3993,7 @@
       <c r="G52" s="57" t="s">
         <v>209</v>
       </c>
-      <c r="H52" s="70"/>
+      <c r="H52" s="66"/>
       <c r="I52" s="43" t="s">
         <v>195</v>
       </c>
@@ -4025,7 +4025,7 @@
       <c r="G53" s="57" t="s">
         <v>198</v>
       </c>
-      <c r="H53" s="70" t="s">
+      <c r="H53" s="66" t="s">
         <v>258</v>
       </c>
       <c r="I53" s="43" t="s">
@@ -4059,7 +4059,7 @@
       <c r="G54" s="57" t="s">
         <v>198</v>
       </c>
-      <c r="H54" s="70" t="s">
+      <c r="H54" s="66" t="s">
         <v>299</v>
       </c>
       <c r="I54" s="43" t="s">
@@ -4093,7 +4093,7 @@
       <c r="G55" s="57" t="s">
         <v>198</v>
       </c>
-      <c r="H55" s="70" t="s">
+      <c r="H55" s="66" t="s">
         <v>346</v>
       </c>
       <c r="I55" s="47" t="s">
@@ -4127,7 +4127,7 @@
       <c r="G56" s="57" t="s">
         <v>198</v>
       </c>
-      <c r="H56" s="70" t="s">
+      <c r="H56" s="66" t="s">
         <v>346</v>
       </c>
       <c r="I56" s="47" t="s">
@@ -4161,7 +4161,7 @@
       <c r="G57" s="57" t="s">
         <v>198</v>
       </c>
-      <c r="H57" s="70" t="s">
+      <c r="H57" s="66" t="s">
         <v>294</v>
       </c>
       <c r="I57" s="47" t="s">
@@ -4198,7 +4198,7 @@
       <c r="G58" s="44" t="s">
         <v>197</v>
       </c>
-      <c r="H58" s="69" t="s">
+      <c r="H58" s="65" t="s">
         <v>252</v>
       </c>
       <c r="I58" s="47" t="s">
@@ -4232,7 +4232,7 @@
       <c r="G59" s="44" t="s">
         <v>197</v>
       </c>
-      <c r="H59" s="69">
+      <c r="H59" s="65">
         <v>7.3</v>
       </c>
       <c r="I59" s="47" t="s">
@@ -4266,7 +4266,7 @@
       <c r="G60" s="44" t="s">
         <v>198</v>
       </c>
-      <c r="H60" s="69" t="s">
+      <c r="H60" s="65" t="s">
         <v>258</v>
       </c>
       <c r="I60" s="47" t="s">
@@ -4300,7 +4300,7 @@
       <c r="G61" s="44" t="s">
         <v>198</v>
       </c>
-      <c r="H61" s="69" t="s">
+      <c r="H61" s="65" t="s">
         <v>258</v>
       </c>
       <c r="I61" s="47" t="s">
@@ -4365,7 +4365,7 @@
       <c r="G63" s="44" t="s">
         <v>198</v>
       </c>
-      <c r="H63" s="69" t="s">
+      <c r="H63" s="65" t="s">
         <v>347</v>
       </c>
       <c r="I63" s="47" t="s">
@@ -4399,7 +4399,7 @@
       <c r="G64" s="57" t="s">
         <v>198</v>
       </c>
-      <c r="H64" s="71" t="s">
+      <c r="H64" s="67" t="s">
         <v>349</v>
       </c>
       <c r="I64" s="47" t="s">
@@ -4433,7 +4433,7 @@
       <c r="G65" s="52" t="s">
         <v>198</v>
       </c>
-      <c r="H65" s="69" t="s">
+      <c r="H65" s="65" t="s">
         <v>309</v>
       </c>
       <c r="I65" s="47" t="s">
@@ -4467,7 +4467,7 @@
       <c r="G66" s="52" t="s">
         <v>198</v>
       </c>
-      <c r="H66" s="69" t="s">
+      <c r="H66" s="65" t="s">
         <v>309</v>
       </c>
       <c r="I66" s="47" t="s">
@@ -4501,7 +4501,7 @@
       <c r="G67" s="52" t="s">
         <v>198</v>
       </c>
-      <c r="H67" s="69" t="s">
+      <c r="H67" s="65" t="s">
         <v>315</v>
       </c>
       <c r="I67" s="47" t="s">
@@ -4530,7 +4530,10 @@
         <v>319</v>
       </c>
       <c r="G68" s="44" t="s">
-        <v>209</v>
+        <v>198</v>
+      </c>
+      <c r="H68" s="65" t="s">
+        <v>349</v>
       </c>
       <c r="I68" s="47" t="s">
         <v>195</v>
@@ -4561,7 +4564,10 @@
         <v>323</v>
       </c>
       <c r="G69" s="44" t="s">
-        <v>209</v>
+        <v>198</v>
+      </c>
+      <c r="H69" s="65" t="s">
+        <v>349</v>
       </c>
       <c r="I69" s="47" t="s">
         <v>195</v>
@@ -4761,7 +4767,7 @@
     <row r="135" ht="12.75"/>
     <row r="136" ht="12.75"/>
     <row r="137" ht="12.75"/>
-    <row r="138"/>
+    <row r="138" ht="12.75"/>
   </sheetData>
   <autoFilter ref="K1:K112" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <dataValidations count="1">
